--- a/data/arac-kullanim-sablon.xlsx
+++ b/data/arac-kullanim-sablon.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{751DC6AE-7EFE-4974-826E-35651F465601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5132B41-8190-4708-8149-9796051E9E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="22104" windowHeight="10572" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ÇİZELGE" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="34">
   <si>
     <t>GÜNLÜK ARAÇ KULLANIMI TAKİP ÇİZELGESİ</t>
   </si>
@@ -138,48 +138,15 @@
     <t>İMZA</t>
   </si>
   <si>
-    <t>KÜBRA ÇOBAN</t>
-  </si>
-  <si>
-    <t>2026-08-07</t>
-  </si>
-  <si>
-    <t>34 KNR 404</t>
-  </si>
-  <si>
     <t>■ Kontrol Edildi.
 □ Uygun değil.
 □ Diğer…...............</t>
   </si>
   <si>
-    <t>Hayır</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
-    <t xml:space="preserve">
-(1. Sefer)</t>
-  </si>
-  <si>
     <t/>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>1111</t>
-  </si>
-  <si>
-    <t>06:58 - 19:58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-(2. Sefer)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-(3. Sefer)</t>
   </si>
   <si>
     <r>
@@ -738,6 +705,63 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -797,63 +821,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1209,243 +1176,243 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A1" s="24"/>
-      <c r="B1" s="24"/>
-      <c r="C1" s="25" t="s">
+      <c r="A1" s="43"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="26" t="s">
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="O1" s="26"/>
+      <c r="O1" s="45"/>
       <c r="P1" s="5" t="s">
         <v>2</v>
       </c>
       <c r="Q1" s="4"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A2" s="24"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="26" t="s">
+      <c r="A2" s="43"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="44"/>
+      <c r="M2" s="44"/>
+      <c r="N2" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="O2" s="26"/>
+      <c r="O2" s="45"/>
       <c r="P2" s="6">
         <v>43635</v>
       </c>
       <c r="Q2" s="7"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" s="24"/>
-      <c r="B3" s="24"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="25"/>
-      <c r="N3" s="26" t="s">
+      <c r="A3" s="43"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="44"/>
+      <c r="K3" s="44"/>
+      <c r="L3" s="44"/>
+      <c r="M3" s="44"/>
+      <c r="N3" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="O3" s="26"/>
+      <c r="O3" s="45"/>
       <c r="P3" s="5" t="s">
         <v>5</v>
       </c>
       <c r="Q3" s="4"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="24"/>
-      <c r="B4" s="24"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="26" t="s">
+      <c r="A4" s="43"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="44"/>
+      <c r="K4" s="44"/>
+      <c r="L4" s="44"/>
+      <c r="M4" s="44"/>
+      <c r="N4" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="O4" s="26"/>
+      <c r="O4" s="45"/>
       <c r="P4" s="6">
         <v>44690</v>
       </c>
       <c r="Q4" s="7"/>
     </row>
     <row r="5" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="27"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27" t="s">
+      <c r="B5" s="46"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-      <c r="I5" s="27"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="46"/>
       <c r="J5" s="9"/>
-      <c r="K5" s="28" t="s">
+      <c r="K5" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="L5" s="29"/>
-      <c r="M5" s="30"/>
-      <c r="N5" s="30"/>
-      <c r="O5" s="30"/>
-      <c r="P5" s="31"/>
+      <c r="L5" s="48"/>
+      <c r="M5" s="49"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="50"/>
       <c r="Q5" s="10"/>
     </row>
     <row r="6" spans="1:17" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="27"/>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
-      <c r="H6" s="27"/>
-      <c r="I6" s="27"/>
+      <c r="A6" s="46"/>
+      <c r="B6" s="46"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="46"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="46"/>
       <c r="J6" s="11"/>
-      <c r="K6" s="32"/>
-      <c r="L6" s="33"/>
-      <c r="M6" s="33"/>
-      <c r="N6" s="33"/>
-      <c r="O6" s="33"/>
-      <c r="P6" s="34"/>
+      <c r="K6" s="51"/>
+      <c r="L6" s="52"/>
+      <c r="M6" s="52"/>
+      <c r="N6" s="52"/>
+      <c r="O6" s="52"/>
+      <c r="P6" s="53"/>
       <c r="Q6" s="10"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" s="27"/>
-      <c r="B7" s="27"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="27"/>
-      <c r="I7" s="27"/>
+      <c r="A7" s="46"/>
+      <c r="B7" s="46"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="46"/>
+      <c r="H7" s="46"/>
+      <c r="I7" s="46"/>
       <c r="J7" s="12"/>
-      <c r="K7" s="35" t="s">
+      <c r="K7" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="36"/>
-      <c r="M7" s="36"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="36"/>
-      <c r="P7" s="37"/>
+      <c r="L7" s="55"/>
+      <c r="M7" s="55"/>
+      <c r="N7" s="55"/>
+      <c r="O7" s="55"/>
+      <c r="P7" s="56"/>
       <c r="Q7" s="13"/>
     </row>
     <row r="8" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27"/>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
-      <c r="I8" s="27"/>
+      <c r="A8" s="46"/>
+      <c r="B8" s="46"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="46"/>
       <c r="J8" s="9"/>
-      <c r="K8" s="38" t="s">
+      <c r="K8" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="L8" s="39"/>
-      <c r="M8" s="40"/>
-      <c r="N8" s="38" t="s">
+      <c r="L8" s="58"/>
+      <c r="M8" s="59"/>
+      <c r="N8" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="O8" s="39"/>
-      <c r="P8" s="40"/>
+      <c r="O8" s="58"/>
+      <c r="P8" s="59"/>
       <c r="Q8" s="8"/>
     </row>
     <row r="9" spans="1:17" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="27"/>
-      <c r="B9" s="27"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="27"/>
+      <c r="A9" s="46"/>
+      <c r="B9" s="46"/>
+      <c r="C9" s="46"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="46"/>
       <c r="J9" s="11"/>
-      <c r="K9" s="41"/>
-      <c r="L9" s="42"/>
-      <c r="M9" s="43"/>
-      <c r="N9" s="41"/>
-      <c r="O9" s="42"/>
-      <c r="P9" s="43"/>
+      <c r="K9" s="60"/>
+      <c r="L9" s="61"/>
+      <c r="M9" s="62"/>
+      <c r="N9" s="60"/>
+      <c r="O9" s="61"/>
+      <c r="P9" s="62"/>
       <c r="Q9" s="8"/>
     </row>
     <row r="10" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="44" t="s">
+      <c r="A10" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="45"/>
-      <c r="C10" s="44" t="s">
+      <c r="B10" s="29"/>
+      <c r="C10" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="45"/>
-      <c r="E10" s="61" t="s">
+      <c r="D10" s="29"/>
+      <c r="E10" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="48" t="s">
+      <c r="F10" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="49"/>
-      <c r="H10" s="49"/>
-      <c r="I10" s="49"/>
-      <c r="J10" s="49"/>
-      <c r="K10" s="49"/>
-      <c r="L10" s="50"/>
-      <c r="M10" s="51" t="s">
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="33"/>
+      <c r="J10" s="33"/>
+      <c r="K10" s="33"/>
+      <c r="L10" s="34"/>
+      <c r="M10" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="N10" s="52"/>
-      <c r="O10" s="53" t="s">
+      <c r="N10" s="36"/>
+      <c r="O10" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="P10" s="54"/>
+      <c r="P10" s="38"/>
       <c r="Q10" s="14"/>
     </row>
     <row r="11" spans="1:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="46"/>
-      <c r="B11" s="47"/>
-      <c r="C11" s="46"/>
-      <c r="D11" s="47"/>
-      <c r="E11" s="62"/>
+      <c r="A11" s="30"/>
+      <c r="B11" s="31"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="42"/>
       <c r="F11" s="15" t="s">
         <v>19</v>
       </c>
@@ -1473,5324 +1440,4745 @@
       <c r="N11" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="O11" s="55"/>
-      <c r="P11" s="56"/>
+      <c r="O11" s="39"/>
+      <c r="P11" s="40"/>
       <c r="Q11" s="17" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="57" t="s">
+      <c r="A12" s="24"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="58"/>
-      <c r="C12" s="57" t="s">
+      <c r="G12" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="H12" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="58"/>
-      <c r="E12" s="18" t="s">
+      <c r="K12" s="2"/>
+      <c r="L12" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="H12" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="J12" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="M12" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="N12" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O12" s="57" t="s">
-        <v>39</v>
-      </c>
-      <c r="P12" s="58"/>
+      <c r="M12" s="18"/>
+      <c r="N12" s="18"/>
+      <c r="O12" s="24"/>
+      <c r="P12" s="25"/>
       <c r="Q12" s="3"/>
     </row>
     <row r="13" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="59" t="s">
+      <c r="A13" s="26"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="60"/>
-      <c r="C13" s="59" t="s">
+      <c r="G13" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="I13" s="22"/>
+      <c r="J13" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="60"/>
-      <c r="E13" s="21" t="s">
+      <c r="K13" s="23"/>
+      <c r="L13" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="G13" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="H13" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="I13" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="J13" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="K13" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="L13" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="M13" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="N13" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="O13" s="59" t="s">
-        <v>39</v>
-      </c>
-      <c r="P13" s="60"/>
+      <c r="M13" s="21"/>
+      <c r="N13" s="21"/>
+      <c r="O13" s="26"/>
+      <c r="P13" s="27"/>
       <c r="Q13" s="23"/>
     </row>
     <row r="14" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="57" t="s">
+      <c r="A14" s="24"/>
+      <c r="B14" s="25"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="58"/>
-      <c r="C14" s="57" t="s">
+      <c r="G14" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="H14" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="I14" s="20"/>
+      <c r="J14" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="58"/>
-      <c r="E14" s="18" t="s">
+      <c r="K14" s="2"/>
+      <c r="L14" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F14" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="G14" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="H14" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="I14" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="J14" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="M14" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="N14" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O14" s="57" t="s">
-        <v>39</v>
-      </c>
-      <c r="P14" s="58"/>
+      <c r="M14" s="18"/>
+      <c r="N14" s="18"/>
+      <c r="O14" s="24"/>
+      <c r="P14" s="25"/>
       <c r="Q14" s="3"/>
     </row>
     <row r="15" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="59"/>
-      <c r="B15" s="60"/>
-      <c r="C15" s="59"/>
-      <c r="D15" s="60"/>
+      <c r="A15" s="26"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="27"/>
       <c r="E15" s="21"/>
       <c r="F15" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G15" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H15" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I15" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J15" s="22"/>
       <c r="K15" s="23"/>
       <c r="L15" s="23"/>
       <c r="M15" s="21"/>
       <c r="N15" s="21"/>
-      <c r="O15" s="59"/>
-      <c r="P15" s="60"/>
+      <c r="O15" s="26"/>
+      <c r="P15" s="27"/>
       <c r="Q15" s="23"/>
     </row>
     <row r="16" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="57"/>
-      <c r="B16" s="58"/>
-      <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
+      <c r="A16" s="24"/>
+      <c r="B16" s="25"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="25"/>
       <c r="E16" s="18"/>
       <c r="F16" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G16" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H16" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I16" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J16" s="20"/>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
       <c r="M16" s="18"/>
       <c r="N16" s="18"/>
-      <c r="O16" s="57"/>
-      <c r="P16" s="58"/>
+      <c r="O16" s="24"/>
+      <c r="P16" s="25"/>
       <c r="Q16" s="3"/>
     </row>
     <row r="17" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="59"/>
-      <c r="B17" s="60"/>
-      <c r="C17" s="59"/>
-      <c r="D17" s="60"/>
+      <c r="A17" s="26"/>
+      <c r="B17" s="27"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="27"/>
       <c r="E17" s="21"/>
       <c r="F17" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G17" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H17" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I17" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J17" s="22"/>
       <c r="K17" s="23"/>
       <c r="L17" s="23"/>
       <c r="M17" s="21"/>
       <c r="N17" s="21"/>
-      <c r="O17" s="59"/>
-      <c r="P17" s="60"/>
+      <c r="O17" s="26"/>
+      <c r="P17" s="27"/>
       <c r="Q17" s="23"/>
     </row>
     <row r="18" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="57"/>
-      <c r="B18" s="58"/>
-      <c r="C18" s="57"/>
-      <c r="D18" s="58"/>
+      <c r="A18" s="24"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="25"/>
       <c r="E18" s="18"/>
       <c r="F18" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G18" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H18" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I18" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J18" s="20"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="18"/>
       <c r="N18" s="18"/>
-      <c r="O18" s="57"/>
-      <c r="P18" s="58"/>
+      <c r="O18" s="24"/>
+      <c r="P18" s="25"/>
       <c r="Q18" s="3"/>
     </row>
     <row r="19" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="59"/>
-      <c r="B19" s="60"/>
-      <c r="C19" s="59"/>
-      <c r="D19" s="60"/>
+      <c r="A19" s="26"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="27"/>
       <c r="E19" s="21"/>
       <c r="F19" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G19" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H19" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I19" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J19" s="22"/>
       <c r="K19" s="23"/>
       <c r="L19" s="23"/>
       <c r="M19" s="21"/>
       <c r="N19" s="21"/>
-      <c r="O19" s="59"/>
-      <c r="P19" s="60"/>
+      <c r="O19" s="26"/>
+      <c r="P19" s="27"/>
       <c r="Q19" s="23"/>
     </row>
     <row r="20" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="57"/>
-      <c r="B20" s="58"/>
-      <c r="C20" s="57"/>
-      <c r="D20" s="58"/>
+      <c r="A20" s="24"/>
+      <c r="B20" s="25"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="25"/>
       <c r="E20" s="18"/>
       <c r="F20" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G20" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H20" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I20" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J20" s="20"/>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
       <c r="M20" s="18"/>
       <c r="N20" s="18"/>
-      <c r="O20" s="57"/>
-      <c r="P20" s="58"/>
+      <c r="O20" s="24"/>
+      <c r="P20" s="25"/>
       <c r="Q20" s="3"/>
     </row>
     <row r="21" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="59"/>
-      <c r="B21" s="60"/>
-      <c r="C21" s="59"/>
-      <c r="D21" s="60"/>
+      <c r="A21" s="26"/>
+      <c r="B21" s="27"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="27"/>
       <c r="E21" s="21"/>
       <c r="F21" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G21" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H21" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I21" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J21" s="22"/>
       <c r="K21" s="23"/>
       <c r="L21" s="23"/>
       <c r="M21" s="21"/>
       <c r="N21" s="21"/>
-      <c r="O21" s="59"/>
-      <c r="P21" s="60"/>
+      <c r="O21" s="26"/>
+      <c r="P21" s="27"/>
       <c r="Q21" s="23"/>
     </row>
     <row r="22" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="57"/>
-      <c r="B22" s="58"/>
-      <c r="C22" s="57"/>
-      <c r="D22" s="58"/>
+      <c r="A22" s="24"/>
+      <c r="B22" s="25"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="25"/>
       <c r="E22" s="18"/>
       <c r="F22" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G22" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H22" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I22" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J22" s="20"/>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
       <c r="M22" s="18"/>
       <c r="N22" s="18"/>
-      <c r="O22" s="57"/>
-      <c r="P22" s="58"/>
+      <c r="O22" s="24"/>
+      <c r="P22" s="25"/>
       <c r="Q22" s="3"/>
     </row>
     <row r="23" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="59"/>
-      <c r="B23" s="60"/>
-      <c r="C23" s="59"/>
-      <c r="D23" s="60"/>
+      <c r="A23" s="26"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="27"/>
       <c r="E23" s="21"/>
       <c r="F23" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G23" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H23" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I23" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J23" s="22"/>
       <c r="K23" s="23"/>
       <c r="L23" s="23"/>
       <c r="M23" s="21"/>
       <c r="N23" s="21"/>
-      <c r="O23" s="59"/>
-      <c r="P23" s="60"/>
+      <c r="O23" s="26"/>
+      <c r="P23" s="27"/>
       <c r="Q23" s="23"/>
     </row>
     <row r="24" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="57"/>
-      <c r="B24" s="58"/>
-      <c r="C24" s="57"/>
-      <c r="D24" s="58"/>
+      <c r="A24" s="24"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="25"/>
       <c r="E24" s="18"/>
       <c r="F24" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G24" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H24" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I24" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J24" s="20"/>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
       <c r="M24" s="18"/>
       <c r="N24" s="18"/>
-      <c r="O24" s="57"/>
-      <c r="P24" s="58"/>
+      <c r="O24" s="24"/>
+      <c r="P24" s="25"/>
       <c r="Q24" s="3"/>
     </row>
     <row r="25" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="59"/>
-      <c r="B25" s="60"/>
-      <c r="C25" s="59"/>
-      <c r="D25" s="60"/>
+      <c r="A25" s="26"/>
+      <c r="B25" s="27"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="27"/>
       <c r="E25" s="21"/>
       <c r="F25" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G25" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H25" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I25" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J25" s="22"/>
       <c r="K25" s="23"/>
       <c r="L25" s="23"/>
       <c r="M25" s="21"/>
       <c r="N25" s="21"/>
-      <c r="O25" s="59"/>
-      <c r="P25" s="60"/>
+      <c r="O25" s="26"/>
+      <c r="P25" s="27"/>
       <c r="Q25" s="23"/>
     </row>
     <row r="26" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="57"/>
-      <c r="B26" s="58"/>
-      <c r="C26" s="57"/>
-      <c r="D26" s="58"/>
+      <c r="A26" s="24"/>
+      <c r="B26" s="25"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="25"/>
       <c r="E26" s="18"/>
       <c r="F26" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G26" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H26" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I26" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J26" s="20"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
       <c r="M26" s="18"/>
       <c r="N26" s="18"/>
-      <c r="O26" s="57"/>
-      <c r="P26" s="58"/>
+      <c r="O26" s="24"/>
+      <c r="P26" s="25"/>
       <c r="Q26" s="3"/>
     </row>
     <row r="27" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="59"/>
-      <c r="B27" s="60"/>
-      <c r="C27" s="59"/>
-      <c r="D27" s="60"/>
+      <c r="A27" s="26"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="27"/>
       <c r="E27" s="21"/>
       <c r="F27" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G27" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H27" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I27" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J27" s="22"/>
       <c r="K27" s="23"/>
       <c r="L27" s="23"/>
       <c r="M27" s="21"/>
       <c r="N27" s="21"/>
-      <c r="O27" s="59"/>
-      <c r="P27" s="60"/>
+      <c r="O27" s="26"/>
+      <c r="P27" s="27"/>
       <c r="Q27" s="23"/>
     </row>
     <row r="28" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="57"/>
-      <c r="B28" s="58"/>
-      <c r="C28" s="57"/>
-      <c r="D28" s="58"/>
+      <c r="A28" s="24"/>
+      <c r="B28" s="25"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="25"/>
       <c r="E28" s="18"/>
       <c r="F28" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G28" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H28" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I28" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J28" s="20"/>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
       <c r="M28" s="18"/>
       <c r="N28" s="18"/>
-      <c r="O28" s="57"/>
-      <c r="P28" s="58"/>
+      <c r="O28" s="24"/>
+      <c r="P28" s="25"/>
       <c r="Q28" s="3"/>
     </row>
     <row r="29" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="59"/>
-      <c r="B29" s="60"/>
-      <c r="C29" s="59"/>
-      <c r="D29" s="60"/>
+      <c r="A29" s="26"/>
+      <c r="B29" s="27"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="27"/>
       <c r="E29" s="21"/>
       <c r="F29" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G29" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H29" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I29" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J29" s="22"/>
       <c r="K29" s="23"/>
       <c r="L29" s="23"/>
       <c r="M29" s="21"/>
       <c r="N29" s="21"/>
-      <c r="O29" s="59"/>
-      <c r="P29" s="60"/>
+      <c r="O29" s="26"/>
+      <c r="P29" s="27"/>
       <c r="Q29" s="23"/>
     </row>
     <row r="30" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="57"/>
-      <c r="B30" s="58"/>
-      <c r="C30" s="57"/>
-      <c r="D30" s="58"/>
+      <c r="A30" s="24"/>
+      <c r="B30" s="25"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="25"/>
       <c r="E30" s="18"/>
       <c r="F30" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G30" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H30" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I30" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J30" s="20"/>
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
       <c r="M30" s="18"/>
       <c r="N30" s="18"/>
-      <c r="O30" s="57"/>
-      <c r="P30" s="58"/>
+      <c r="O30" s="24"/>
+      <c r="P30" s="25"/>
       <c r="Q30" s="3"/>
     </row>
     <row r="31" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="59"/>
-      <c r="B31" s="60"/>
-      <c r="C31" s="59"/>
-      <c r="D31" s="60"/>
+      <c r="A31" s="26"/>
+      <c r="B31" s="27"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="27"/>
       <c r="E31" s="21"/>
       <c r="F31" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G31" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H31" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I31" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J31" s="22"/>
       <c r="K31" s="23"/>
       <c r="L31" s="23"/>
       <c r="M31" s="21"/>
       <c r="N31" s="21"/>
-      <c r="O31" s="59"/>
-      <c r="P31" s="60"/>
+      <c r="O31" s="26"/>
+      <c r="P31" s="27"/>
       <c r="Q31" s="23"/>
     </row>
     <row r="32" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="57"/>
-      <c r="B32" s="58"/>
-      <c r="C32" s="57"/>
-      <c r="D32" s="58"/>
+      <c r="A32" s="24"/>
+      <c r="B32" s="25"/>
+      <c r="C32" s="24"/>
+      <c r="D32" s="25"/>
       <c r="E32" s="18"/>
       <c r="F32" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H32" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I32" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J32" s="20"/>
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
       <c r="M32" s="18"/>
       <c r="N32" s="18"/>
-      <c r="O32" s="57"/>
-      <c r="P32" s="58"/>
+      <c r="O32" s="24"/>
+      <c r="P32" s="25"/>
       <c r="Q32" s="3"/>
     </row>
     <row r="33" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="59"/>
-      <c r="B33" s="60"/>
-      <c r="C33" s="59"/>
-      <c r="D33" s="60"/>
+      <c r="A33" s="26"/>
+      <c r="B33" s="27"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="27"/>
       <c r="E33" s="21"/>
       <c r="F33" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G33" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H33" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I33" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J33" s="22"/>
       <c r="K33" s="23"/>
       <c r="L33" s="23"/>
       <c r="M33" s="21"/>
       <c r="N33" s="21"/>
-      <c r="O33" s="59"/>
-      <c r="P33" s="60"/>
+      <c r="O33" s="26"/>
+      <c r="P33" s="27"/>
       <c r="Q33" s="23"/>
     </row>
     <row r="34" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="57"/>
-      <c r="B34" s="58"/>
-      <c r="C34" s="57"/>
-      <c r="D34" s="58"/>
+      <c r="A34" s="24"/>
+      <c r="B34" s="25"/>
+      <c r="C34" s="24"/>
+      <c r="D34" s="25"/>
       <c r="E34" s="18"/>
       <c r="F34" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G34" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H34" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I34" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J34" s="20"/>
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
       <c r="M34" s="18"/>
       <c r="N34" s="18"/>
-      <c r="O34" s="57"/>
-      <c r="P34" s="58"/>
+      <c r="O34" s="24"/>
+      <c r="P34" s="25"/>
       <c r="Q34" s="3"/>
     </row>
     <row r="35" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="59"/>
-      <c r="B35" s="60"/>
-      <c r="C35" s="59"/>
-      <c r="D35" s="60"/>
+      <c r="A35" s="26"/>
+      <c r="B35" s="27"/>
+      <c r="C35" s="26"/>
+      <c r="D35" s="27"/>
       <c r="E35" s="21"/>
       <c r="F35" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G35" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H35" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I35" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J35" s="22"/>
       <c r="K35" s="23"/>
       <c r="L35" s="23"/>
       <c r="M35" s="21"/>
       <c r="N35" s="21"/>
-      <c r="O35" s="59"/>
-      <c r="P35" s="60"/>
+      <c r="O35" s="26"/>
+      <c r="P35" s="27"/>
       <c r="Q35" s="23"/>
     </row>
     <row r="36" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="57"/>
-      <c r="B36" s="58"/>
-      <c r="C36" s="57"/>
-      <c r="D36" s="58"/>
+      <c r="A36" s="24"/>
+      <c r="B36" s="25"/>
+      <c r="C36" s="24"/>
+      <c r="D36" s="25"/>
       <c r="E36" s="18"/>
       <c r="F36" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G36" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H36" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I36" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J36" s="20"/>
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
       <c r="M36" s="18"/>
       <c r="N36" s="18"/>
-      <c r="O36" s="57"/>
-      <c r="P36" s="58"/>
+      <c r="O36" s="24"/>
+      <c r="P36" s="25"/>
       <c r="Q36" s="3"/>
     </row>
     <row r="37" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="59"/>
-      <c r="B37" s="60"/>
-      <c r="C37" s="59"/>
-      <c r="D37" s="60"/>
+      <c r="A37" s="26"/>
+      <c r="B37" s="27"/>
+      <c r="C37" s="26"/>
+      <c r="D37" s="27"/>
       <c r="E37" s="21"/>
       <c r="F37" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G37" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H37" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I37" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J37" s="22"/>
       <c r="K37" s="23"/>
       <c r="L37" s="23"/>
       <c r="M37" s="21"/>
       <c r="N37" s="21"/>
-      <c r="O37" s="59"/>
-      <c r="P37" s="60"/>
+      <c r="O37" s="26"/>
+      <c r="P37" s="27"/>
       <c r="Q37" s="23"/>
     </row>
     <row r="38" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="57"/>
-      <c r="B38" s="58"/>
-      <c r="C38" s="57"/>
-      <c r="D38" s="58"/>
+      <c r="A38" s="24"/>
+      <c r="B38" s="25"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="25"/>
       <c r="E38" s="18"/>
       <c r="F38" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G38" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H38" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I38" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J38" s="20"/>
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
       <c r="M38" s="18"/>
       <c r="N38" s="18"/>
-      <c r="O38" s="57"/>
-      <c r="P38" s="58"/>
+      <c r="O38" s="24"/>
+      <c r="P38" s="25"/>
       <c r="Q38" s="3"/>
     </row>
     <row r="39" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="59"/>
-      <c r="B39" s="60"/>
-      <c r="C39" s="59"/>
-      <c r="D39" s="60"/>
+      <c r="A39" s="26"/>
+      <c r="B39" s="27"/>
+      <c r="C39" s="26"/>
+      <c r="D39" s="27"/>
       <c r="E39" s="21"/>
       <c r="F39" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G39" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H39" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I39" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J39" s="22"/>
       <c r="K39" s="23"/>
       <c r="L39" s="23"/>
       <c r="M39" s="21"/>
       <c r="N39" s="21"/>
-      <c r="O39" s="59"/>
-      <c r="P39" s="60"/>
+      <c r="O39" s="26"/>
+      <c r="P39" s="27"/>
       <c r="Q39" s="23"/>
     </row>
     <row r="40" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="57"/>
-      <c r="B40" s="58"/>
-      <c r="C40" s="57"/>
-      <c r="D40" s="58"/>
+      <c r="A40" s="24"/>
+      <c r="B40" s="25"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="25"/>
       <c r="E40" s="18"/>
       <c r="F40" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G40" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H40" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I40" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J40" s="20"/>
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
       <c r="M40" s="18"/>
       <c r="N40" s="18"/>
-      <c r="O40" s="57"/>
-      <c r="P40" s="58"/>
+      <c r="O40" s="24"/>
+      <c r="P40" s="25"/>
       <c r="Q40" s="3"/>
     </row>
     <row r="41" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="59"/>
-      <c r="B41" s="60"/>
-      <c r="C41" s="59"/>
-      <c r="D41" s="60"/>
+      <c r="A41" s="26"/>
+      <c r="B41" s="27"/>
+      <c r="C41" s="26"/>
+      <c r="D41" s="27"/>
       <c r="E41" s="21"/>
       <c r="F41" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G41" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H41" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I41" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J41" s="22"/>
       <c r="K41" s="23"/>
       <c r="L41" s="23"/>
       <c r="M41" s="21"/>
       <c r="N41" s="21"/>
-      <c r="O41" s="59"/>
-      <c r="P41" s="60"/>
+      <c r="O41" s="26"/>
+      <c r="P41" s="27"/>
       <c r="Q41" s="23"/>
     </row>
     <row r="42" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="57"/>
-      <c r="B42" s="58"/>
-      <c r="C42" s="57"/>
-      <c r="D42" s="58"/>
+      <c r="A42" s="24"/>
+      <c r="B42" s="25"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="25"/>
       <c r="E42" s="18"/>
       <c r="F42" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G42" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H42" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I42" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J42" s="20"/>
       <c r="K42" s="2"/>
       <c r="L42" s="2"/>
       <c r="M42" s="18"/>
       <c r="N42" s="18"/>
-      <c r="O42" s="57"/>
-      <c r="P42" s="58"/>
+      <c r="O42" s="24"/>
+      <c r="P42" s="25"/>
       <c r="Q42" s="3"/>
     </row>
     <row r="43" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="59"/>
-      <c r="B43" s="60"/>
-      <c r="C43" s="59"/>
-      <c r="D43" s="60"/>
+      <c r="A43" s="26"/>
+      <c r="B43" s="27"/>
+      <c r="C43" s="26"/>
+      <c r="D43" s="27"/>
       <c r="E43" s="21"/>
       <c r="F43" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G43" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H43" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I43" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J43" s="22"/>
       <c r="K43" s="23"/>
       <c r="L43" s="23"/>
       <c r="M43" s="21"/>
       <c r="N43" s="21"/>
-      <c r="O43" s="59"/>
-      <c r="P43" s="60"/>
+      <c r="O43" s="26"/>
+      <c r="P43" s="27"/>
       <c r="Q43" s="23"/>
     </row>
     <row r="44" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="57"/>
-      <c r="B44" s="58"/>
-      <c r="C44" s="57"/>
-      <c r="D44" s="58"/>
+      <c r="A44" s="24"/>
+      <c r="B44" s="25"/>
+      <c r="C44" s="24"/>
+      <c r="D44" s="25"/>
       <c r="E44" s="18"/>
       <c r="F44" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G44" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H44" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I44" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J44" s="20"/>
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
       <c r="M44" s="18"/>
       <c r="N44" s="18"/>
-      <c r="O44" s="57"/>
-      <c r="P44" s="58"/>
+      <c r="O44" s="24"/>
+      <c r="P44" s="25"/>
       <c r="Q44" s="3"/>
     </row>
     <row r="45" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="59"/>
-      <c r="B45" s="60"/>
-      <c r="C45" s="59"/>
-      <c r="D45" s="60"/>
+      <c r="A45" s="26"/>
+      <c r="B45" s="27"/>
+      <c r="C45" s="26"/>
+      <c r="D45" s="27"/>
       <c r="E45" s="21"/>
       <c r="F45" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H45" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I45" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J45" s="22"/>
       <c r="K45" s="23"/>
       <c r="L45" s="23"/>
       <c r="M45" s="21"/>
       <c r="N45" s="21"/>
-      <c r="O45" s="59"/>
-      <c r="P45" s="60"/>
+      <c r="O45" s="26"/>
+      <c r="P45" s="27"/>
       <c r="Q45" s="23"/>
     </row>
     <row r="46" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="57"/>
-      <c r="B46" s="58"/>
-      <c r="C46" s="57"/>
-      <c r="D46" s="58"/>
+      <c r="A46" s="24"/>
+      <c r="B46" s="25"/>
+      <c r="C46" s="24"/>
+      <c r="D46" s="25"/>
       <c r="E46" s="18"/>
       <c r="F46" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G46" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H46" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I46" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J46" s="20"/>
       <c r="K46" s="2"/>
       <c r="L46" s="2"/>
       <c r="M46" s="18"/>
       <c r="N46" s="18"/>
-      <c r="O46" s="57"/>
-      <c r="P46" s="58"/>
+      <c r="O46" s="24"/>
+      <c r="P46" s="25"/>
       <c r="Q46" s="3"/>
     </row>
     <row r="47" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="59"/>
-      <c r="B47" s="60"/>
-      <c r="C47" s="59"/>
-      <c r="D47" s="60"/>
+      <c r="A47" s="26"/>
+      <c r="B47" s="27"/>
+      <c r="C47" s="26"/>
+      <c r="D47" s="27"/>
       <c r="E47" s="21"/>
       <c r="F47" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G47" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H47" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I47" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J47" s="22"/>
       <c r="K47" s="23"/>
       <c r="L47" s="23"/>
       <c r="M47" s="21"/>
       <c r="N47" s="21"/>
-      <c r="O47" s="59"/>
-      <c r="P47" s="60"/>
+      <c r="O47" s="26"/>
+      <c r="P47" s="27"/>
       <c r="Q47" s="23"/>
     </row>
     <row r="48" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="57"/>
-      <c r="B48" s="58"/>
-      <c r="C48" s="57"/>
-      <c r="D48" s="58"/>
+      <c r="A48" s="24"/>
+      <c r="B48" s="25"/>
+      <c r="C48" s="24"/>
+      <c r="D48" s="25"/>
       <c r="E48" s="18"/>
       <c r="F48" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G48" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H48" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I48" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J48" s="20"/>
       <c r="K48" s="2"/>
       <c r="L48" s="2"/>
       <c r="M48" s="18"/>
       <c r="N48" s="18"/>
-      <c r="O48" s="57"/>
-      <c r="P48" s="58"/>
+      <c r="O48" s="24"/>
+      <c r="P48" s="25"/>
       <c r="Q48" s="3"/>
     </row>
     <row r="49" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="59"/>
-      <c r="B49" s="60"/>
-      <c r="C49" s="59"/>
-      <c r="D49" s="60"/>
+      <c r="A49" s="26"/>
+      <c r="B49" s="27"/>
+      <c r="C49" s="26"/>
+      <c r="D49" s="27"/>
       <c r="E49" s="21"/>
       <c r="F49" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G49" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H49" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I49" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J49" s="22"/>
       <c r="K49" s="23"/>
       <c r="L49" s="23"/>
       <c r="M49" s="21"/>
       <c r="N49" s="21"/>
-      <c r="O49" s="59"/>
-      <c r="P49" s="60"/>
+      <c r="O49" s="26"/>
+      <c r="P49" s="27"/>
       <c r="Q49" s="23"/>
     </row>
     <row r="50" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="57"/>
-      <c r="B50" s="58"/>
-      <c r="C50" s="57"/>
-      <c r="D50" s="58"/>
+      <c r="A50" s="24"/>
+      <c r="B50" s="25"/>
+      <c r="C50" s="24"/>
+      <c r="D50" s="25"/>
       <c r="E50" s="18"/>
       <c r="F50" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G50" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H50" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I50" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J50" s="20"/>
       <c r="K50" s="2"/>
       <c r="L50" s="2"/>
       <c r="M50" s="18"/>
       <c r="N50" s="18"/>
-      <c r="O50" s="57"/>
-      <c r="P50" s="58"/>
+      <c r="O50" s="24"/>
+      <c r="P50" s="25"/>
       <c r="Q50" s="3"/>
     </row>
     <row r="51" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="59"/>
-      <c r="B51" s="60"/>
-      <c r="C51" s="59"/>
-      <c r="D51" s="60"/>
+      <c r="A51" s="26"/>
+      <c r="B51" s="27"/>
+      <c r="C51" s="26"/>
+      <c r="D51" s="27"/>
       <c r="E51" s="21"/>
       <c r="F51" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G51" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H51" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I51" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J51" s="22"/>
       <c r="K51" s="23"/>
       <c r="L51" s="23"/>
       <c r="M51" s="21"/>
       <c r="N51" s="21"/>
-      <c r="O51" s="59"/>
-      <c r="P51" s="60"/>
+      <c r="O51" s="26"/>
+      <c r="P51" s="27"/>
       <c r="Q51" s="23"/>
     </row>
     <row r="52" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="57"/>
-      <c r="B52" s="58"/>
-      <c r="C52" s="57"/>
-      <c r="D52" s="58"/>
+      <c r="A52" s="24"/>
+      <c r="B52" s="25"/>
+      <c r="C52" s="24"/>
+      <c r="D52" s="25"/>
       <c r="E52" s="18"/>
       <c r="F52" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G52" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H52" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I52" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J52" s="20"/>
       <c r="K52" s="2"/>
       <c r="L52" s="2"/>
       <c r="M52" s="18"/>
       <c r="N52" s="18"/>
-      <c r="O52" s="57"/>
-      <c r="P52" s="58"/>
+      <c r="O52" s="24"/>
+      <c r="P52" s="25"/>
       <c r="Q52" s="3"/>
     </row>
     <row r="53" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="59"/>
-      <c r="B53" s="60"/>
-      <c r="C53" s="59"/>
-      <c r="D53" s="60"/>
+      <c r="A53" s="26"/>
+      <c r="B53" s="27"/>
+      <c r="C53" s="26"/>
+      <c r="D53" s="27"/>
       <c r="E53" s="21"/>
       <c r="F53" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G53" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H53" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I53" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J53" s="22"/>
       <c r="K53" s="23"/>
       <c r="L53" s="23"/>
       <c r="M53" s="21"/>
       <c r="N53" s="21"/>
-      <c r="O53" s="59"/>
-      <c r="P53" s="60"/>
+      <c r="O53" s="26"/>
+      <c r="P53" s="27"/>
       <c r="Q53" s="23"/>
     </row>
     <row r="54" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="57"/>
-      <c r="B54" s="58"/>
-      <c r="C54" s="57"/>
-      <c r="D54" s="58"/>
+      <c r="A54" s="24"/>
+      <c r="B54" s="25"/>
+      <c r="C54" s="24"/>
+      <c r="D54" s="25"/>
       <c r="E54" s="18"/>
       <c r="F54" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G54" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H54" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I54" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J54" s="20"/>
       <c r="K54" s="2"/>
       <c r="L54" s="2"/>
       <c r="M54" s="18"/>
       <c r="N54" s="18"/>
-      <c r="O54" s="57"/>
-      <c r="P54" s="58"/>
+      <c r="O54" s="24"/>
+      <c r="P54" s="25"/>
       <c r="Q54" s="3"/>
     </row>
     <row r="55" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="59"/>
-      <c r="B55" s="60"/>
-      <c r="C55" s="59"/>
-      <c r="D55" s="60"/>
+      <c r="A55" s="26"/>
+      <c r="B55" s="27"/>
+      <c r="C55" s="26"/>
+      <c r="D55" s="27"/>
       <c r="E55" s="21"/>
       <c r="F55" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H55" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I55" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J55" s="22"/>
       <c r="K55" s="23"/>
       <c r="L55" s="23"/>
       <c r="M55" s="21"/>
       <c r="N55" s="21"/>
-      <c r="O55" s="59"/>
-      <c r="P55" s="60"/>
+      <c r="O55" s="26"/>
+      <c r="P55" s="27"/>
       <c r="Q55" s="23"/>
     </row>
     <row r="56" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="57"/>
-      <c r="B56" s="58"/>
-      <c r="C56" s="57"/>
-      <c r="D56" s="58"/>
+      <c r="A56" s="24"/>
+      <c r="B56" s="25"/>
+      <c r="C56" s="24"/>
+      <c r="D56" s="25"/>
       <c r="E56" s="18"/>
       <c r="F56" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G56" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H56" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I56" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J56" s="20"/>
       <c r="K56" s="2"/>
       <c r="L56" s="2"/>
       <c r="M56" s="18"/>
       <c r="N56" s="18"/>
-      <c r="O56" s="57"/>
-      <c r="P56" s="58"/>
+      <c r="O56" s="24"/>
+      <c r="P56" s="25"/>
       <c r="Q56" s="3"/>
     </row>
     <row r="57" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="59"/>
-      <c r="B57" s="60"/>
-      <c r="C57" s="59"/>
-      <c r="D57" s="60"/>
+      <c r="A57" s="26"/>
+      <c r="B57" s="27"/>
+      <c r="C57" s="26"/>
+      <c r="D57" s="27"/>
       <c r="E57" s="21"/>
       <c r="F57" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G57" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H57" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I57" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J57" s="22"/>
       <c r="K57" s="23"/>
       <c r="L57" s="23"/>
       <c r="M57" s="21"/>
       <c r="N57" s="21"/>
-      <c r="O57" s="59"/>
-      <c r="P57" s="60"/>
+      <c r="O57" s="26"/>
+      <c r="P57" s="27"/>
       <c r="Q57" s="23"/>
     </row>
     <row r="58" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="57"/>
-      <c r="B58" s="58"/>
-      <c r="C58" s="57"/>
-      <c r="D58" s="58"/>
+      <c r="A58" s="24"/>
+      <c r="B58" s="25"/>
+      <c r="C58" s="24"/>
+      <c r="D58" s="25"/>
       <c r="E58" s="18"/>
       <c r="F58" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G58" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H58" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I58" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J58" s="20"/>
       <c r="K58" s="2"/>
       <c r="L58" s="2"/>
       <c r="M58" s="18"/>
       <c r="N58" s="18"/>
-      <c r="O58" s="57"/>
-      <c r="P58" s="58"/>
+      <c r="O58" s="24"/>
+      <c r="P58" s="25"/>
       <c r="Q58" s="3"/>
     </row>
     <row r="59" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="59"/>
-      <c r="B59" s="60"/>
-      <c r="C59" s="59"/>
-      <c r="D59" s="60"/>
+      <c r="A59" s="26"/>
+      <c r="B59" s="27"/>
+      <c r="C59" s="26"/>
+      <c r="D59" s="27"/>
       <c r="E59" s="21"/>
       <c r="F59" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H59" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I59" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J59" s="22"/>
       <c r="K59" s="23"/>
       <c r="L59" s="23"/>
       <c r="M59" s="21"/>
       <c r="N59" s="21"/>
-      <c r="O59" s="59"/>
-      <c r="P59" s="60"/>
+      <c r="O59" s="26"/>
+      <c r="P59" s="27"/>
       <c r="Q59" s="23"/>
     </row>
     <row r="60" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="57"/>
-      <c r="B60" s="58"/>
-      <c r="C60" s="57"/>
-      <c r="D60" s="58"/>
+      <c r="A60" s="24"/>
+      <c r="B60" s="25"/>
+      <c r="C60" s="24"/>
+      <c r="D60" s="25"/>
       <c r="E60" s="18"/>
       <c r="F60" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G60" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H60" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I60" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J60" s="20"/>
       <c r="K60" s="2"/>
       <c r="L60" s="2"/>
       <c r="M60" s="18"/>
       <c r="N60" s="18"/>
-      <c r="O60" s="57"/>
-      <c r="P60" s="58"/>
+      <c r="O60" s="24"/>
+      <c r="P60" s="25"/>
       <c r="Q60" s="3"/>
     </row>
     <row r="61" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="59"/>
-      <c r="B61" s="60"/>
-      <c r="C61" s="59"/>
-      <c r="D61" s="60"/>
+      <c r="A61" s="26"/>
+      <c r="B61" s="27"/>
+      <c r="C61" s="26"/>
+      <c r="D61" s="27"/>
       <c r="E61" s="21"/>
       <c r="F61" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G61" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H61" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I61" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J61" s="22"/>
       <c r="K61" s="23"/>
       <c r="L61" s="23"/>
       <c r="M61" s="21"/>
       <c r="N61" s="21"/>
-      <c r="O61" s="59"/>
-      <c r="P61" s="60"/>
+      <c r="O61" s="26"/>
+      <c r="P61" s="27"/>
       <c r="Q61" s="23"/>
     </row>
     <row r="62" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="57"/>
-      <c r="B62" s="58"/>
-      <c r="C62" s="57"/>
-      <c r="D62" s="58"/>
+      <c r="A62" s="24"/>
+      <c r="B62" s="25"/>
+      <c r="C62" s="24"/>
+      <c r="D62" s="25"/>
       <c r="E62" s="18"/>
       <c r="F62" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G62" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H62" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I62" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J62" s="20"/>
       <c r="K62" s="2"/>
       <c r="L62" s="2"/>
       <c r="M62" s="18"/>
       <c r="N62" s="18"/>
-      <c r="O62" s="57"/>
-      <c r="P62" s="58"/>
+      <c r="O62" s="24"/>
+      <c r="P62" s="25"/>
       <c r="Q62" s="3"/>
     </row>
     <row r="63" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="59"/>
-      <c r="B63" s="60"/>
-      <c r="C63" s="59"/>
-      <c r="D63" s="60"/>
+      <c r="A63" s="26"/>
+      <c r="B63" s="27"/>
+      <c r="C63" s="26"/>
+      <c r="D63" s="27"/>
       <c r="E63" s="21"/>
       <c r="F63" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G63" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H63" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I63" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J63" s="22"/>
       <c r="K63" s="23"/>
       <c r="L63" s="23"/>
       <c r="M63" s="21"/>
       <c r="N63" s="21"/>
-      <c r="O63" s="59"/>
-      <c r="P63" s="60"/>
+      <c r="O63" s="26"/>
+      <c r="P63" s="27"/>
       <c r="Q63" s="23"/>
     </row>
     <row r="64" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="57"/>
-      <c r="B64" s="58"/>
-      <c r="C64" s="57"/>
-      <c r="D64" s="58"/>
+      <c r="A64" s="24"/>
+      <c r="B64" s="25"/>
+      <c r="C64" s="24"/>
+      <c r="D64" s="25"/>
       <c r="E64" s="18"/>
       <c r="F64" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G64" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H64" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I64" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J64" s="20"/>
       <c r="K64" s="2"/>
       <c r="L64" s="2"/>
       <c r="M64" s="18"/>
       <c r="N64" s="18"/>
-      <c r="O64" s="57"/>
-      <c r="P64" s="58"/>
+      <c r="O64" s="24"/>
+      <c r="P64" s="25"/>
       <c r="Q64" s="3"/>
     </row>
     <row r="65" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="59"/>
-      <c r="B65" s="60"/>
-      <c r="C65" s="59"/>
-      <c r="D65" s="60"/>
+      <c r="A65" s="26"/>
+      <c r="B65" s="27"/>
+      <c r="C65" s="26"/>
+      <c r="D65" s="27"/>
       <c r="E65" s="21"/>
       <c r="F65" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G65" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H65" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I65" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J65" s="22"/>
       <c r="K65" s="23"/>
       <c r="L65" s="23"/>
       <c r="M65" s="21"/>
       <c r="N65" s="21"/>
-      <c r="O65" s="59"/>
-      <c r="P65" s="60"/>
+      <c r="O65" s="26"/>
+      <c r="P65" s="27"/>
       <c r="Q65" s="23"/>
     </row>
     <row r="66" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="57"/>
-      <c r="B66" s="58"/>
-      <c r="C66" s="57"/>
-      <c r="D66" s="58"/>
+      <c r="A66" s="24"/>
+      <c r="B66" s="25"/>
+      <c r="C66" s="24"/>
+      <c r="D66" s="25"/>
       <c r="E66" s="18"/>
       <c r="F66" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G66" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H66" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I66" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J66" s="20"/>
       <c r="K66" s="2"/>
       <c r="L66" s="2"/>
       <c r="M66" s="18"/>
       <c r="N66" s="18"/>
-      <c r="O66" s="57"/>
-      <c r="P66" s="58"/>
+      <c r="O66" s="24"/>
+      <c r="P66" s="25"/>
       <c r="Q66" s="3"/>
     </row>
     <row r="67" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="59"/>
-      <c r="B67" s="60"/>
-      <c r="C67" s="59"/>
-      <c r="D67" s="60"/>
+      <c r="A67" s="26"/>
+      <c r="B67" s="27"/>
+      <c r="C67" s="26"/>
+      <c r="D67" s="27"/>
       <c r="E67" s="21"/>
       <c r="F67" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G67" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H67" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I67" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J67" s="22"/>
       <c r="K67" s="23"/>
       <c r="L67" s="23"/>
       <c r="M67" s="21"/>
       <c r="N67" s="21"/>
-      <c r="O67" s="59"/>
-      <c r="P67" s="60"/>
+      <c r="O67" s="26"/>
+      <c r="P67" s="27"/>
       <c r="Q67" s="23"/>
     </row>
     <row r="68" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="57"/>
-      <c r="B68" s="58"/>
-      <c r="C68" s="57"/>
-      <c r="D68" s="58"/>
+      <c r="A68" s="24"/>
+      <c r="B68" s="25"/>
+      <c r="C68" s="24"/>
+      <c r="D68" s="25"/>
       <c r="E68" s="18"/>
       <c r="F68" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H68" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I68" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J68" s="20"/>
       <c r="K68" s="2"/>
       <c r="L68" s="2"/>
       <c r="M68" s="18"/>
       <c r="N68" s="18"/>
-      <c r="O68" s="57"/>
-      <c r="P68" s="58"/>
+      <c r="O68" s="24"/>
+      <c r="P68" s="25"/>
       <c r="Q68" s="3"/>
     </row>
     <row r="69" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="59"/>
-      <c r="B69" s="60"/>
-      <c r="C69" s="59"/>
-      <c r="D69" s="60"/>
+      <c r="A69" s="26"/>
+      <c r="B69" s="27"/>
+      <c r="C69" s="26"/>
+      <c r="D69" s="27"/>
       <c r="E69" s="21"/>
       <c r="F69" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G69" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H69" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I69" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J69" s="22"/>
       <c r="K69" s="23"/>
       <c r="L69" s="23"/>
       <c r="M69" s="21"/>
       <c r="N69" s="21"/>
-      <c r="O69" s="59"/>
-      <c r="P69" s="60"/>
+      <c r="O69" s="26"/>
+      <c r="P69" s="27"/>
       <c r="Q69" s="23"/>
     </row>
     <row r="70" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="57"/>
-      <c r="B70" s="58"/>
-      <c r="C70" s="57"/>
-      <c r="D70" s="58"/>
+      <c r="A70" s="24"/>
+      <c r="B70" s="25"/>
+      <c r="C70" s="24"/>
+      <c r="D70" s="25"/>
       <c r="E70" s="18"/>
       <c r="F70" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G70" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H70" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I70" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J70" s="20"/>
       <c r="K70" s="2"/>
       <c r="L70" s="2"/>
       <c r="M70" s="18"/>
       <c r="N70" s="18"/>
-      <c r="O70" s="57"/>
-      <c r="P70" s="58"/>
+      <c r="O70" s="24"/>
+      <c r="P70" s="25"/>
       <c r="Q70" s="3"/>
     </row>
     <row r="71" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="59"/>
-      <c r="B71" s="60"/>
-      <c r="C71" s="59"/>
-      <c r="D71" s="60"/>
+      <c r="A71" s="26"/>
+      <c r="B71" s="27"/>
+      <c r="C71" s="26"/>
+      <c r="D71" s="27"/>
       <c r="E71" s="21"/>
       <c r="F71" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G71" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H71" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I71" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J71" s="22"/>
       <c r="K71" s="23"/>
       <c r="L71" s="23"/>
       <c r="M71" s="21"/>
       <c r="N71" s="21"/>
-      <c r="O71" s="59"/>
-      <c r="P71" s="60"/>
+      <c r="O71" s="26"/>
+      <c r="P71" s="27"/>
       <c r="Q71" s="23"/>
     </row>
     <row r="72" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="57"/>
-      <c r="B72" s="58"/>
-      <c r="C72" s="57"/>
-      <c r="D72" s="58"/>
+      <c r="A72" s="24"/>
+      <c r="B72" s="25"/>
+      <c r="C72" s="24"/>
+      <c r="D72" s="25"/>
       <c r="E72" s="18"/>
       <c r="F72" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G72" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H72" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I72" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J72" s="20"/>
       <c r="K72" s="2"/>
       <c r="L72" s="2"/>
       <c r="M72" s="18"/>
       <c r="N72" s="18"/>
-      <c r="O72" s="57"/>
-      <c r="P72" s="58"/>
+      <c r="O72" s="24"/>
+      <c r="P72" s="25"/>
       <c r="Q72" s="3"/>
     </row>
     <row r="73" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="59"/>
-      <c r="B73" s="60"/>
-      <c r="C73" s="59"/>
-      <c r="D73" s="60"/>
+      <c r="A73" s="26"/>
+      <c r="B73" s="27"/>
+      <c r="C73" s="26"/>
+      <c r="D73" s="27"/>
       <c r="E73" s="21"/>
       <c r="F73" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G73" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H73" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I73" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J73" s="22"/>
       <c r="K73" s="23"/>
       <c r="L73" s="23"/>
       <c r="M73" s="21"/>
       <c r="N73" s="21"/>
-      <c r="O73" s="59"/>
-      <c r="P73" s="60"/>
+      <c r="O73" s="26"/>
+      <c r="P73" s="27"/>
       <c r="Q73" s="23"/>
     </row>
     <row r="74" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="57"/>
-      <c r="B74" s="58"/>
-      <c r="C74" s="57"/>
-      <c r="D74" s="58"/>
+      <c r="A74" s="24"/>
+      <c r="B74" s="25"/>
+      <c r="C74" s="24"/>
+      <c r="D74" s="25"/>
       <c r="E74" s="18"/>
       <c r="F74" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G74" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H74" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I74" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J74" s="20"/>
       <c r="K74" s="2"/>
       <c r="L74" s="2"/>
       <c r="M74" s="18"/>
       <c r="N74" s="18"/>
-      <c r="O74" s="57"/>
-      <c r="P74" s="58"/>
+      <c r="O74" s="24"/>
+      <c r="P74" s="25"/>
       <c r="Q74" s="3"/>
     </row>
     <row r="75" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="59"/>
-      <c r="B75" s="60"/>
-      <c r="C75" s="59"/>
-      <c r="D75" s="60"/>
+      <c r="A75" s="26"/>
+      <c r="B75" s="27"/>
+      <c r="C75" s="26"/>
+      <c r="D75" s="27"/>
       <c r="E75" s="21"/>
       <c r="F75" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G75" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H75" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I75" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J75" s="22"/>
       <c r="K75" s="23"/>
       <c r="L75" s="23"/>
       <c r="M75" s="21"/>
       <c r="N75" s="21"/>
-      <c r="O75" s="59"/>
-      <c r="P75" s="60"/>
+      <c r="O75" s="26"/>
+      <c r="P75" s="27"/>
       <c r="Q75" s="23"/>
     </row>
     <row r="76" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="57"/>
-      <c r="B76" s="58"/>
-      <c r="C76" s="57"/>
-      <c r="D76" s="58"/>
+      <c r="A76" s="24"/>
+      <c r="B76" s="25"/>
+      <c r="C76" s="24"/>
+      <c r="D76" s="25"/>
       <c r="E76" s="18"/>
       <c r="F76" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G76" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H76" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I76" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J76" s="20"/>
       <c r="K76" s="2"/>
       <c r="L76" s="2"/>
       <c r="M76" s="18"/>
       <c r="N76" s="18"/>
-      <c r="O76" s="57"/>
-      <c r="P76" s="58"/>
+      <c r="O76" s="24"/>
+      <c r="P76" s="25"/>
       <c r="Q76" s="3"/>
     </row>
     <row r="77" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="59"/>
-      <c r="B77" s="60"/>
-      <c r="C77" s="59"/>
-      <c r="D77" s="60"/>
+      <c r="A77" s="26"/>
+      <c r="B77" s="27"/>
+      <c r="C77" s="26"/>
+      <c r="D77" s="27"/>
       <c r="E77" s="21"/>
       <c r="F77" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G77" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H77" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I77" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J77" s="22"/>
       <c r="K77" s="23"/>
       <c r="L77" s="23"/>
       <c r="M77" s="21"/>
       <c r="N77" s="21"/>
-      <c r="O77" s="59"/>
-      <c r="P77" s="60"/>
+      <c r="O77" s="26"/>
+      <c r="P77" s="27"/>
       <c r="Q77" s="23"/>
     </row>
     <row r="78" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="57"/>
-      <c r="B78" s="58"/>
-      <c r="C78" s="57"/>
-      <c r="D78" s="58"/>
+      <c r="A78" s="24"/>
+      <c r="B78" s="25"/>
+      <c r="C78" s="24"/>
+      <c r="D78" s="25"/>
       <c r="E78" s="18"/>
       <c r="F78" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G78" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H78" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I78" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J78" s="20"/>
       <c r="K78" s="2"/>
       <c r="L78" s="2"/>
       <c r="M78" s="18"/>
       <c r="N78" s="18"/>
-      <c r="O78" s="57"/>
-      <c r="P78" s="58"/>
+      <c r="O78" s="24"/>
+      <c r="P78" s="25"/>
       <c r="Q78" s="3"/>
     </row>
     <row r="79" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="59"/>
-      <c r="B79" s="60"/>
-      <c r="C79" s="59"/>
-      <c r="D79" s="60"/>
+      <c r="A79" s="26"/>
+      <c r="B79" s="27"/>
+      <c r="C79" s="26"/>
+      <c r="D79" s="27"/>
       <c r="E79" s="21"/>
       <c r="F79" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G79" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H79" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I79" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J79" s="22"/>
       <c r="K79" s="23"/>
       <c r="L79" s="23"/>
       <c r="M79" s="21"/>
       <c r="N79" s="21"/>
-      <c r="O79" s="59"/>
-      <c r="P79" s="60"/>
+      <c r="O79" s="26"/>
+      <c r="P79" s="27"/>
       <c r="Q79" s="23"/>
     </row>
     <row r="80" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="57"/>
-      <c r="B80" s="58"/>
-      <c r="C80" s="57"/>
-      <c r="D80" s="58"/>
+      <c r="A80" s="24"/>
+      <c r="B80" s="25"/>
+      <c r="C80" s="24"/>
+      <c r="D80" s="25"/>
       <c r="E80" s="18"/>
       <c r="F80" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H80" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I80" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J80" s="20"/>
       <c r="K80" s="2"/>
       <c r="L80" s="2"/>
       <c r="M80" s="18"/>
       <c r="N80" s="18"/>
-      <c r="O80" s="57"/>
-      <c r="P80" s="58"/>
+      <c r="O80" s="24"/>
+      <c r="P80" s="25"/>
       <c r="Q80" s="3"/>
     </row>
     <row r="81" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="59"/>
-      <c r="B81" s="60"/>
-      <c r="C81" s="59"/>
-      <c r="D81" s="60"/>
+      <c r="A81" s="26"/>
+      <c r="B81" s="27"/>
+      <c r="C81" s="26"/>
+      <c r="D81" s="27"/>
       <c r="E81" s="21"/>
       <c r="F81" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G81" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H81" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I81" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J81" s="22"/>
       <c r="K81" s="23"/>
       <c r="L81" s="23"/>
       <c r="M81" s="21"/>
       <c r="N81" s="21"/>
-      <c r="O81" s="59"/>
-      <c r="P81" s="60"/>
+      <c r="O81" s="26"/>
+      <c r="P81" s="27"/>
       <c r="Q81" s="23"/>
     </row>
     <row r="82" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="57"/>
-      <c r="B82" s="58"/>
-      <c r="C82" s="57"/>
-      <c r="D82" s="58"/>
+      <c r="A82" s="24"/>
+      <c r="B82" s="25"/>
+      <c r="C82" s="24"/>
+      <c r="D82" s="25"/>
       <c r="E82" s="18"/>
       <c r="F82" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G82" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H82" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I82" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J82" s="20"/>
       <c r="K82" s="2"/>
       <c r="L82" s="2"/>
       <c r="M82" s="18"/>
       <c r="N82" s="18"/>
-      <c r="O82" s="57"/>
-      <c r="P82" s="58"/>
+      <c r="O82" s="24"/>
+      <c r="P82" s="25"/>
       <c r="Q82" s="3"/>
     </row>
     <row r="83" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="59"/>
-      <c r="B83" s="60"/>
-      <c r="C83" s="59"/>
-      <c r="D83" s="60"/>
+      <c r="A83" s="26"/>
+      <c r="B83" s="27"/>
+      <c r="C83" s="26"/>
+      <c r="D83" s="27"/>
       <c r="E83" s="21"/>
       <c r="F83" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G83" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H83" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I83" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J83" s="22"/>
       <c r="K83" s="23"/>
       <c r="L83" s="23"/>
       <c r="M83" s="21"/>
       <c r="N83" s="21"/>
-      <c r="O83" s="59"/>
-      <c r="P83" s="60"/>
+      <c r="O83" s="26"/>
+      <c r="P83" s="27"/>
       <c r="Q83" s="23"/>
     </row>
     <row r="84" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="57"/>
-      <c r="B84" s="58"/>
-      <c r="C84" s="57"/>
-      <c r="D84" s="58"/>
+      <c r="A84" s="24"/>
+      <c r="B84" s="25"/>
+      <c r="C84" s="24"/>
+      <c r="D84" s="25"/>
       <c r="E84" s="18"/>
       <c r="F84" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G84" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H84" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I84" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J84" s="20"/>
       <c r="K84" s="2"/>
       <c r="L84" s="2"/>
       <c r="M84" s="18"/>
       <c r="N84" s="18"/>
-      <c r="O84" s="57"/>
-      <c r="P84" s="58"/>
+      <c r="O84" s="24"/>
+      <c r="P84" s="25"/>
       <c r="Q84" s="3"/>
     </row>
     <row r="85" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="59"/>
-      <c r="B85" s="60"/>
-      <c r="C85" s="59"/>
-      <c r="D85" s="60"/>
+      <c r="A85" s="26"/>
+      <c r="B85" s="27"/>
+      <c r="C85" s="26"/>
+      <c r="D85" s="27"/>
       <c r="E85" s="21"/>
       <c r="F85" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G85" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H85" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I85" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J85" s="22"/>
       <c r="K85" s="23"/>
       <c r="L85" s="23"/>
       <c r="M85" s="21"/>
       <c r="N85" s="21"/>
-      <c r="O85" s="59"/>
-      <c r="P85" s="60"/>
+      <c r="O85" s="26"/>
+      <c r="P85" s="27"/>
       <c r="Q85" s="23"/>
     </row>
     <row r="86" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="57"/>
-      <c r="B86" s="58"/>
-      <c r="C86" s="57"/>
-      <c r="D86" s="58"/>
+      <c r="A86" s="24"/>
+      <c r="B86" s="25"/>
+      <c r="C86" s="24"/>
+      <c r="D86" s="25"/>
       <c r="E86" s="18"/>
       <c r="F86" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G86" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H86" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I86" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J86" s="20"/>
       <c r="K86" s="2"/>
       <c r="L86" s="2"/>
       <c r="M86" s="18"/>
       <c r="N86" s="18"/>
-      <c r="O86" s="57"/>
-      <c r="P86" s="58"/>
+      <c r="O86" s="24"/>
+      <c r="P86" s="25"/>
       <c r="Q86" s="3"/>
     </row>
     <row r="87" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="59"/>
-      <c r="B87" s="60"/>
-      <c r="C87" s="59"/>
-      <c r="D87" s="60"/>
+      <c r="A87" s="26"/>
+      <c r="B87" s="27"/>
+      <c r="C87" s="26"/>
+      <c r="D87" s="27"/>
       <c r="E87" s="21"/>
       <c r="F87" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G87" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H87" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I87" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J87" s="22"/>
       <c r="K87" s="23"/>
       <c r="L87" s="23"/>
       <c r="M87" s="21"/>
       <c r="N87" s="21"/>
-      <c r="O87" s="59"/>
-      <c r="P87" s="60"/>
+      <c r="O87" s="26"/>
+      <c r="P87" s="27"/>
       <c r="Q87" s="23"/>
     </row>
     <row r="88" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="57"/>
-      <c r="B88" s="58"/>
-      <c r="C88" s="57"/>
-      <c r="D88" s="58"/>
+      <c r="A88" s="24"/>
+      <c r="B88" s="25"/>
+      <c r="C88" s="24"/>
+      <c r="D88" s="25"/>
       <c r="E88" s="18"/>
       <c r="F88" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G88" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H88" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I88" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J88" s="20"/>
       <c r="K88" s="2"/>
       <c r="L88" s="2"/>
       <c r="M88" s="18"/>
       <c r="N88" s="18"/>
-      <c r="O88" s="57"/>
-      <c r="P88" s="58"/>
+      <c r="O88" s="24"/>
+      <c r="P88" s="25"/>
       <c r="Q88" s="3"/>
     </row>
     <row r="89" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="59"/>
-      <c r="B89" s="60"/>
-      <c r="C89" s="59"/>
-      <c r="D89" s="60"/>
+      <c r="A89" s="26"/>
+      <c r="B89" s="27"/>
+      <c r="C89" s="26"/>
+      <c r="D89" s="27"/>
       <c r="E89" s="21"/>
       <c r="F89" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G89" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H89" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I89" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J89" s="22"/>
       <c r="K89" s="23"/>
       <c r="L89" s="23"/>
       <c r="M89" s="21"/>
       <c r="N89" s="21"/>
-      <c r="O89" s="59"/>
-      <c r="P89" s="60"/>
+      <c r="O89" s="26"/>
+      <c r="P89" s="27"/>
       <c r="Q89" s="23"/>
     </row>
     <row r="90" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="57"/>
-      <c r="B90" s="58"/>
-      <c r="C90" s="57"/>
-      <c r="D90" s="58"/>
+      <c r="A90" s="24"/>
+      <c r="B90" s="25"/>
+      <c r="C90" s="24"/>
+      <c r="D90" s="25"/>
       <c r="E90" s="18"/>
       <c r="F90" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H90" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I90" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J90" s="20"/>
       <c r="K90" s="2"/>
       <c r="L90" s="2"/>
       <c r="M90" s="18"/>
       <c r="N90" s="18"/>
-      <c r="O90" s="57"/>
-      <c r="P90" s="58"/>
+      <c r="O90" s="24"/>
+      <c r="P90" s="25"/>
       <c r="Q90" s="3"/>
     </row>
     <row r="91" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="59"/>
-      <c r="B91" s="60"/>
-      <c r="C91" s="59"/>
-      <c r="D91" s="60"/>
+      <c r="A91" s="26"/>
+      <c r="B91" s="27"/>
+      <c r="C91" s="26"/>
+      <c r="D91" s="27"/>
       <c r="E91" s="21"/>
       <c r="F91" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G91" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H91" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I91" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J91" s="22"/>
       <c r="K91" s="23"/>
       <c r="L91" s="23"/>
       <c r="M91" s="21"/>
       <c r="N91" s="21"/>
-      <c r="O91" s="59"/>
-      <c r="P91" s="60"/>
+      <c r="O91" s="26"/>
+      <c r="P91" s="27"/>
       <c r="Q91" s="23"/>
     </row>
     <row r="92" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="57"/>
-      <c r="B92" s="58"/>
-      <c r="C92" s="57"/>
-      <c r="D92" s="58"/>
+      <c r="A92" s="24"/>
+      <c r="B92" s="25"/>
+      <c r="C92" s="24"/>
+      <c r="D92" s="25"/>
       <c r="E92" s="18"/>
       <c r="F92" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G92" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H92" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I92" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J92" s="20"/>
       <c r="K92" s="2"/>
       <c r="L92" s="2"/>
       <c r="M92" s="18"/>
       <c r="N92" s="18"/>
-      <c r="O92" s="57"/>
-      <c r="P92" s="58"/>
+      <c r="O92" s="24"/>
+      <c r="P92" s="25"/>
       <c r="Q92" s="3"/>
     </row>
     <row r="93" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="59"/>
-      <c r="B93" s="60"/>
-      <c r="C93" s="59"/>
-      <c r="D93" s="60"/>
+      <c r="A93" s="26"/>
+      <c r="B93" s="27"/>
+      <c r="C93" s="26"/>
+      <c r="D93" s="27"/>
       <c r="E93" s="21"/>
       <c r="F93" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G93" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H93" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I93" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J93" s="22"/>
       <c r="K93" s="23"/>
       <c r="L93" s="23"/>
       <c r="M93" s="21"/>
       <c r="N93" s="21"/>
-      <c r="O93" s="59"/>
-      <c r="P93" s="60"/>
+      <c r="O93" s="26"/>
+      <c r="P93" s="27"/>
       <c r="Q93" s="23"/>
     </row>
     <row r="94" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="57"/>
-      <c r="B94" s="58"/>
-      <c r="C94" s="57"/>
-      <c r="D94" s="58"/>
+      <c r="A94" s="24"/>
+      <c r="B94" s="25"/>
+      <c r="C94" s="24"/>
+      <c r="D94" s="25"/>
       <c r="E94" s="18"/>
       <c r="F94" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G94" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H94" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I94" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J94" s="20"/>
       <c r="K94" s="2"/>
       <c r="L94" s="2"/>
       <c r="M94" s="18"/>
       <c r="N94" s="18"/>
-      <c r="O94" s="57"/>
-      <c r="P94" s="58"/>
+      <c r="O94" s="24"/>
+      <c r="P94" s="25"/>
       <c r="Q94" s="3"/>
     </row>
     <row r="95" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="59"/>
-      <c r="B95" s="60"/>
-      <c r="C95" s="59"/>
-      <c r="D95" s="60"/>
+      <c r="A95" s="26"/>
+      <c r="B95" s="27"/>
+      <c r="C95" s="26"/>
+      <c r="D95" s="27"/>
       <c r="E95" s="21"/>
       <c r="F95" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G95" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H95" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I95" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J95" s="22"/>
       <c r="K95" s="23"/>
       <c r="L95" s="23"/>
       <c r="M95" s="21"/>
       <c r="N95" s="21"/>
-      <c r="O95" s="59"/>
-      <c r="P95" s="60"/>
+      <c r="O95" s="26"/>
+      <c r="P95" s="27"/>
       <c r="Q95" s="23"/>
     </row>
     <row r="96" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="57"/>
-      <c r="B96" s="58"/>
-      <c r="C96" s="57"/>
-      <c r="D96" s="58"/>
+      <c r="A96" s="24"/>
+      <c r="B96" s="25"/>
+      <c r="C96" s="24"/>
+      <c r="D96" s="25"/>
       <c r="E96" s="18"/>
       <c r="F96" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G96" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H96" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I96" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J96" s="20"/>
       <c r="K96" s="2"/>
       <c r="L96" s="2"/>
       <c r="M96" s="18"/>
       <c r="N96" s="18"/>
-      <c r="O96" s="57"/>
-      <c r="P96" s="58"/>
+      <c r="O96" s="24"/>
+      <c r="P96" s="25"/>
       <c r="Q96" s="3"/>
     </row>
     <row r="97" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="59"/>
-      <c r="B97" s="60"/>
-      <c r="C97" s="59"/>
-      <c r="D97" s="60"/>
+      <c r="A97" s="26"/>
+      <c r="B97" s="27"/>
+      <c r="C97" s="26"/>
+      <c r="D97" s="27"/>
       <c r="E97" s="21"/>
       <c r="F97" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G97" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H97" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I97" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J97" s="22"/>
       <c r="K97" s="23"/>
       <c r="L97" s="23"/>
       <c r="M97" s="21"/>
       <c r="N97" s="21"/>
-      <c r="O97" s="59"/>
-      <c r="P97" s="60"/>
+      <c r="O97" s="26"/>
+      <c r="P97" s="27"/>
       <c r="Q97" s="23"/>
     </row>
     <row r="98" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="57"/>
-      <c r="B98" s="58"/>
-      <c r="C98" s="57"/>
-      <c r="D98" s="58"/>
+      <c r="A98" s="24"/>
+      <c r="B98" s="25"/>
+      <c r="C98" s="24"/>
+      <c r="D98" s="25"/>
       <c r="E98" s="18"/>
       <c r="F98" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G98" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H98" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I98" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J98" s="20"/>
       <c r="K98" s="2"/>
       <c r="L98" s="2"/>
       <c r="M98" s="18"/>
       <c r="N98" s="18"/>
-      <c r="O98" s="57"/>
-      <c r="P98" s="58"/>
+      <c r="O98" s="24"/>
+      <c r="P98" s="25"/>
       <c r="Q98" s="3"/>
     </row>
     <row r="99" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="59"/>
-      <c r="B99" s="60"/>
-      <c r="C99" s="59"/>
-      <c r="D99" s="60"/>
+      <c r="A99" s="26"/>
+      <c r="B99" s="27"/>
+      <c r="C99" s="26"/>
+      <c r="D99" s="27"/>
       <c r="E99" s="21"/>
       <c r="F99" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G99" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H99" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I99" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J99" s="22"/>
       <c r="K99" s="23"/>
       <c r="L99" s="23"/>
       <c r="M99" s="21"/>
       <c r="N99" s="21"/>
-      <c r="O99" s="59"/>
-      <c r="P99" s="60"/>
+      <c r="O99" s="26"/>
+      <c r="P99" s="27"/>
       <c r="Q99" s="23"/>
     </row>
     <row r="100" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="57"/>
-      <c r="B100" s="58"/>
-      <c r="C100" s="57"/>
-      <c r="D100" s="58"/>
+      <c r="A100" s="24"/>
+      <c r="B100" s="25"/>
+      <c r="C100" s="24"/>
+      <c r="D100" s="25"/>
       <c r="E100" s="18"/>
       <c r="F100" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H100" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I100" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J100" s="20"/>
       <c r="K100" s="2"/>
       <c r="L100" s="2"/>
       <c r="M100" s="18"/>
       <c r="N100" s="18"/>
-      <c r="O100" s="57"/>
-      <c r="P100" s="58"/>
+      <c r="O100" s="24"/>
+      <c r="P100" s="25"/>
       <c r="Q100" s="3"/>
     </row>
     <row r="101" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="59"/>
-      <c r="B101" s="60"/>
-      <c r="C101" s="59"/>
-      <c r="D101" s="60"/>
+      <c r="A101" s="26"/>
+      <c r="B101" s="27"/>
+      <c r="C101" s="26"/>
+      <c r="D101" s="27"/>
       <c r="E101" s="21"/>
       <c r="F101" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G101" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H101" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I101" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J101" s="22"/>
       <c r="K101" s="23"/>
       <c r="L101" s="23"/>
       <c r="M101" s="21"/>
       <c r="N101" s="21"/>
-      <c r="O101" s="59"/>
-      <c r="P101" s="60"/>
+      <c r="O101" s="26"/>
+      <c r="P101" s="27"/>
       <c r="Q101" s="23"/>
     </row>
     <row r="102" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="57"/>
-      <c r="B102" s="58"/>
-      <c r="C102" s="57"/>
-      <c r="D102" s="58"/>
+      <c r="A102" s="24"/>
+      <c r="B102" s="25"/>
+      <c r="C102" s="24"/>
+      <c r="D102" s="25"/>
       <c r="E102" s="18"/>
       <c r="F102" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G102" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H102" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I102" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J102" s="20"/>
       <c r="K102" s="2"/>
       <c r="L102" s="2"/>
       <c r="M102" s="18"/>
       <c r="N102" s="18"/>
-      <c r="O102" s="57"/>
-      <c r="P102" s="58"/>
+      <c r="O102" s="24"/>
+      <c r="P102" s="25"/>
       <c r="Q102" s="3"/>
     </row>
     <row r="103" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="59"/>
-      <c r="B103" s="60"/>
-      <c r="C103" s="59"/>
-      <c r="D103" s="60"/>
+      <c r="A103" s="26"/>
+      <c r="B103" s="27"/>
+      <c r="C103" s="26"/>
+      <c r="D103" s="27"/>
       <c r="E103" s="21"/>
       <c r="F103" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G103" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H103" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I103" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J103" s="22"/>
       <c r="K103" s="23"/>
       <c r="L103" s="23"/>
       <c r="M103" s="21"/>
       <c r="N103" s="21"/>
-      <c r="O103" s="59"/>
-      <c r="P103" s="60"/>
+      <c r="O103" s="26"/>
+      <c r="P103" s="27"/>
       <c r="Q103" s="23"/>
     </row>
     <row r="104" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="57"/>
-      <c r="B104" s="58"/>
-      <c r="C104" s="57"/>
-      <c r="D104" s="58"/>
+      <c r="A104" s="24"/>
+      <c r="B104" s="25"/>
+      <c r="C104" s="24"/>
+      <c r="D104" s="25"/>
       <c r="E104" s="18"/>
       <c r="F104" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H104" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I104" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J104" s="20"/>
       <c r="K104" s="2"/>
       <c r="L104" s="2"/>
       <c r="M104" s="18"/>
       <c r="N104" s="18"/>
-      <c r="O104" s="57"/>
-      <c r="P104" s="58"/>
+      <c r="O104" s="24"/>
+      <c r="P104" s="25"/>
       <c r="Q104" s="3"/>
     </row>
     <row r="105" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="59"/>
-      <c r="B105" s="60"/>
-      <c r="C105" s="59"/>
-      <c r="D105" s="60"/>
+      <c r="A105" s="26"/>
+      <c r="B105" s="27"/>
+      <c r="C105" s="26"/>
+      <c r="D105" s="27"/>
       <c r="E105" s="21"/>
       <c r="F105" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G105" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H105" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I105" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J105" s="22"/>
       <c r="K105" s="23"/>
       <c r="L105" s="23"/>
       <c r="M105" s="21"/>
       <c r="N105" s="21"/>
-      <c r="O105" s="59"/>
-      <c r="P105" s="60"/>
+      <c r="O105" s="26"/>
+      <c r="P105" s="27"/>
       <c r="Q105" s="23"/>
     </row>
     <row r="106" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="57"/>
-      <c r="B106" s="58"/>
-      <c r="C106" s="57"/>
-      <c r="D106" s="58"/>
+      <c r="A106" s="24"/>
+      <c r="B106" s="25"/>
+      <c r="C106" s="24"/>
+      <c r="D106" s="25"/>
       <c r="E106" s="18"/>
       <c r="F106" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G106" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H106" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I106" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J106" s="20"/>
       <c r="K106" s="2"/>
       <c r="L106" s="2"/>
       <c r="M106" s="18"/>
       <c r="N106" s="18"/>
-      <c r="O106" s="57"/>
-      <c r="P106" s="58"/>
+      <c r="O106" s="24"/>
+      <c r="P106" s="25"/>
       <c r="Q106" s="3"/>
     </row>
     <row r="107" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="59"/>
-      <c r="B107" s="60"/>
-      <c r="C107" s="59"/>
-      <c r="D107" s="60"/>
+      <c r="A107" s="26"/>
+      <c r="B107" s="27"/>
+      <c r="C107" s="26"/>
+      <c r="D107" s="27"/>
       <c r="E107" s="21"/>
       <c r="F107" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G107" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H107" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I107" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J107" s="22"/>
       <c r="K107" s="23"/>
       <c r="L107" s="23"/>
       <c r="M107" s="21"/>
       <c r="N107" s="21"/>
-      <c r="O107" s="59"/>
-      <c r="P107" s="60"/>
+      <c r="O107" s="26"/>
+      <c r="P107" s="27"/>
       <c r="Q107" s="23"/>
     </row>
     <row r="108" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="57"/>
-      <c r="B108" s="58"/>
-      <c r="C108" s="57"/>
-      <c r="D108" s="58"/>
+      <c r="A108" s="24"/>
+      <c r="B108" s="25"/>
+      <c r="C108" s="24"/>
+      <c r="D108" s="25"/>
       <c r="E108" s="18"/>
       <c r="F108" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G108" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H108" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I108" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J108" s="20"/>
       <c r="K108" s="2"/>
       <c r="L108" s="2"/>
       <c r="M108" s="18"/>
       <c r="N108" s="18"/>
-      <c r="O108" s="57"/>
-      <c r="P108" s="58"/>
+      <c r="O108" s="24"/>
+      <c r="P108" s="25"/>
       <c r="Q108" s="3"/>
     </row>
     <row r="109" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="59"/>
-      <c r="B109" s="60"/>
-      <c r="C109" s="59"/>
-      <c r="D109" s="60"/>
+      <c r="A109" s="26"/>
+      <c r="B109" s="27"/>
+      <c r="C109" s="26"/>
+      <c r="D109" s="27"/>
       <c r="E109" s="21"/>
       <c r="F109" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G109" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H109" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I109" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J109" s="22"/>
       <c r="K109" s="23"/>
       <c r="L109" s="23"/>
       <c r="M109" s="21"/>
       <c r="N109" s="21"/>
-      <c r="O109" s="59"/>
-      <c r="P109" s="60"/>
+      <c r="O109" s="26"/>
+      <c r="P109" s="27"/>
       <c r="Q109" s="23"/>
     </row>
     <row r="110" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="57"/>
-      <c r="B110" s="58"/>
-      <c r="C110" s="57"/>
-      <c r="D110" s="58"/>
+      <c r="A110" s="24"/>
+      <c r="B110" s="25"/>
+      <c r="C110" s="24"/>
+      <c r="D110" s="25"/>
       <c r="E110" s="18"/>
       <c r="F110" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G110" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H110" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I110" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J110" s="20"/>
       <c r="K110" s="2"/>
       <c r="L110" s="2"/>
       <c r="M110" s="18"/>
       <c r="N110" s="18"/>
-      <c r="O110" s="57"/>
-      <c r="P110" s="58"/>
+      <c r="O110" s="24"/>
+      <c r="P110" s="25"/>
       <c r="Q110" s="3"/>
     </row>
     <row r="111" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="59"/>
-      <c r="B111" s="60"/>
-      <c r="C111" s="59"/>
-      <c r="D111" s="60"/>
+      <c r="A111" s="26"/>
+      <c r="B111" s="27"/>
+      <c r="C111" s="26"/>
+      <c r="D111" s="27"/>
       <c r="E111" s="21"/>
       <c r="F111" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G111" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H111" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I111" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J111" s="22"/>
       <c r="K111" s="23"/>
       <c r="L111" s="23"/>
       <c r="M111" s="21"/>
       <c r="N111" s="21"/>
-      <c r="O111" s="59"/>
-      <c r="P111" s="60"/>
+      <c r="O111" s="26"/>
+      <c r="P111" s="27"/>
       <c r="Q111" s="23"/>
     </row>
     <row r="112" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="57"/>
-      <c r="B112" s="58"/>
-      <c r="C112" s="57"/>
-      <c r="D112" s="58"/>
+      <c r="A112" s="24"/>
+      <c r="B112" s="25"/>
+      <c r="C112" s="24"/>
+      <c r="D112" s="25"/>
       <c r="E112" s="18"/>
       <c r="F112" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G112" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H112" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I112" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J112" s="20"/>
       <c r="K112" s="2"/>
       <c r="L112" s="2"/>
       <c r="M112" s="18"/>
       <c r="N112" s="18"/>
-      <c r="O112" s="57"/>
-      <c r="P112" s="58"/>
+      <c r="O112" s="24"/>
+      <c r="P112" s="25"/>
       <c r="Q112" s="3"/>
     </row>
     <row r="113" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="59"/>
-      <c r="B113" s="60"/>
-      <c r="C113" s="59"/>
-      <c r="D113" s="60"/>
+      <c r="A113" s="26"/>
+      <c r="B113" s="27"/>
+      <c r="C113" s="26"/>
+      <c r="D113" s="27"/>
       <c r="E113" s="21"/>
       <c r="F113" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G113" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H113" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I113" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J113" s="22"/>
       <c r="K113" s="23"/>
       <c r="L113" s="23"/>
       <c r="M113" s="21"/>
       <c r="N113" s="21"/>
-      <c r="O113" s="59"/>
-      <c r="P113" s="60"/>
+      <c r="O113" s="26"/>
+      <c r="P113" s="27"/>
       <c r="Q113" s="23"/>
     </row>
     <row r="114" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="57"/>
-      <c r="B114" s="58"/>
-      <c r="C114" s="57"/>
-      <c r="D114" s="58"/>
+      <c r="A114" s="24"/>
+      <c r="B114" s="25"/>
+      <c r="C114" s="24"/>
+      <c r="D114" s="25"/>
       <c r="E114" s="18"/>
       <c r="F114" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G114" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H114" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I114" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J114" s="20"/>
       <c r="K114" s="2"/>
       <c r="L114" s="2"/>
       <c r="M114" s="18"/>
       <c r="N114" s="18"/>
-      <c r="O114" s="57"/>
-      <c r="P114" s="58"/>
+      <c r="O114" s="24"/>
+      <c r="P114" s="25"/>
       <c r="Q114" s="3"/>
     </row>
     <row r="115" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="59"/>
-      <c r="B115" s="60"/>
-      <c r="C115" s="59"/>
-      <c r="D115" s="60"/>
+      <c r="A115" s="26"/>
+      <c r="B115" s="27"/>
+      <c r="C115" s="26"/>
+      <c r="D115" s="27"/>
       <c r="E115" s="21"/>
       <c r="F115" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G115" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H115" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I115" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J115" s="22"/>
       <c r="K115" s="23"/>
       <c r="L115" s="23"/>
       <c r="M115" s="21"/>
       <c r="N115" s="21"/>
-      <c r="O115" s="59"/>
-      <c r="P115" s="60"/>
+      <c r="O115" s="26"/>
+      <c r="P115" s="27"/>
       <c r="Q115" s="23"/>
     </row>
     <row r="116" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="57"/>
-      <c r="B116" s="58"/>
-      <c r="C116" s="57"/>
-      <c r="D116" s="58"/>
+      <c r="A116" s="24"/>
+      <c r="B116" s="25"/>
+      <c r="C116" s="24"/>
+      <c r="D116" s="25"/>
       <c r="E116" s="18"/>
       <c r="F116" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G116" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H116" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I116" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J116" s="20"/>
       <c r="K116" s="2"/>
       <c r="L116" s="2"/>
       <c r="M116" s="18"/>
       <c r="N116" s="18"/>
-      <c r="O116" s="57"/>
-      <c r="P116" s="58"/>
+      <c r="O116" s="24"/>
+      <c r="P116" s="25"/>
       <c r="Q116" s="3"/>
     </row>
     <row r="117" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="59"/>
-      <c r="B117" s="60"/>
-      <c r="C117" s="59"/>
-      <c r="D117" s="60"/>
+      <c r="A117" s="26"/>
+      <c r="B117" s="27"/>
+      <c r="C117" s="26"/>
+      <c r="D117" s="27"/>
       <c r="E117" s="21"/>
       <c r="F117" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G117" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H117" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I117" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J117" s="22"/>
       <c r="K117" s="23"/>
       <c r="L117" s="23"/>
       <c r="M117" s="21"/>
       <c r="N117" s="21"/>
-      <c r="O117" s="59"/>
-      <c r="P117" s="60"/>
+      <c r="O117" s="26"/>
+      <c r="P117" s="27"/>
       <c r="Q117" s="23"/>
     </row>
     <row r="118" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="57"/>
-      <c r="B118" s="58"/>
-      <c r="C118" s="57"/>
-      <c r="D118" s="58"/>
+      <c r="A118" s="24"/>
+      <c r="B118" s="25"/>
+      <c r="C118" s="24"/>
+      <c r="D118" s="25"/>
       <c r="E118" s="18"/>
       <c r="F118" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H118" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I118" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J118" s="20"/>
       <c r="K118" s="2"/>
       <c r="L118" s="2"/>
       <c r="M118" s="18"/>
       <c r="N118" s="18"/>
-      <c r="O118" s="57"/>
-      <c r="P118" s="58"/>
+      <c r="O118" s="24"/>
+      <c r="P118" s="25"/>
       <c r="Q118" s="3"/>
     </row>
     <row r="119" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="59"/>
-      <c r="B119" s="60"/>
-      <c r="C119" s="59"/>
-      <c r="D119" s="60"/>
+      <c r="A119" s="26"/>
+      <c r="B119" s="27"/>
+      <c r="C119" s="26"/>
+      <c r="D119" s="27"/>
       <c r="E119" s="21"/>
       <c r="F119" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G119" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H119" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I119" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J119" s="22"/>
       <c r="K119" s="23"/>
       <c r="L119" s="23"/>
       <c r="M119" s="21"/>
       <c r="N119" s="21"/>
-      <c r="O119" s="59"/>
-      <c r="P119" s="60"/>
+      <c r="O119" s="26"/>
+      <c r="P119" s="27"/>
       <c r="Q119" s="23"/>
     </row>
     <row r="120" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="57"/>
-      <c r="B120" s="58"/>
-      <c r="C120" s="57"/>
-      <c r="D120" s="58"/>
+      <c r="A120" s="24"/>
+      <c r="B120" s="25"/>
+      <c r="C120" s="24"/>
+      <c r="D120" s="25"/>
       <c r="E120" s="18"/>
       <c r="F120" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G120" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H120" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I120" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J120" s="20"/>
       <c r="K120" s="2"/>
       <c r="L120" s="2"/>
       <c r="M120" s="18"/>
       <c r="N120" s="18"/>
-      <c r="O120" s="57"/>
-      <c r="P120" s="58"/>
+      <c r="O120" s="24"/>
+      <c r="P120" s="25"/>
       <c r="Q120" s="3"/>
     </row>
     <row r="121" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="59"/>
-      <c r="B121" s="60"/>
-      <c r="C121" s="59"/>
-      <c r="D121" s="60"/>
+      <c r="A121" s="26"/>
+      <c r="B121" s="27"/>
+      <c r="C121" s="26"/>
+      <c r="D121" s="27"/>
       <c r="E121" s="21"/>
       <c r="F121" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G121" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H121" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I121" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J121" s="22"/>
       <c r="K121" s="23"/>
       <c r="L121" s="23"/>
       <c r="M121" s="21"/>
       <c r="N121" s="21"/>
-      <c r="O121" s="59"/>
-      <c r="P121" s="60"/>
+      <c r="O121" s="26"/>
+      <c r="P121" s="27"/>
       <c r="Q121" s="23"/>
     </row>
     <row r="122" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="57"/>
-      <c r="B122" s="58"/>
-      <c r="C122" s="57"/>
-      <c r="D122" s="58"/>
+      <c r="A122" s="24"/>
+      <c r="B122" s="25"/>
+      <c r="C122" s="24"/>
+      <c r="D122" s="25"/>
       <c r="E122" s="18"/>
       <c r="F122" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G122" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H122" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I122" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J122" s="20"/>
       <c r="K122" s="2"/>
       <c r="L122" s="2"/>
       <c r="M122" s="18"/>
       <c r="N122" s="18"/>
-      <c r="O122" s="57"/>
-      <c r="P122" s="58"/>
+      <c r="O122" s="24"/>
+      <c r="P122" s="25"/>
       <c r="Q122" s="3"/>
     </row>
     <row r="123" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="59"/>
-      <c r="B123" s="60"/>
-      <c r="C123" s="59"/>
-      <c r="D123" s="60"/>
+      <c r="A123" s="26"/>
+      <c r="B123" s="27"/>
+      <c r="C123" s="26"/>
+      <c r="D123" s="27"/>
       <c r="E123" s="21"/>
       <c r="F123" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G123" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H123" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I123" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J123" s="22"/>
       <c r="K123" s="23"/>
       <c r="L123" s="23"/>
       <c r="M123" s="21"/>
       <c r="N123" s="21"/>
-      <c r="O123" s="59"/>
-      <c r="P123" s="60"/>
+      <c r="O123" s="26"/>
+      <c r="P123" s="27"/>
       <c r="Q123" s="23"/>
     </row>
     <row r="124" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="57"/>
-      <c r="B124" s="58"/>
-      <c r="C124" s="57"/>
-      <c r="D124" s="58"/>
+      <c r="A124" s="24"/>
+      <c r="B124" s="25"/>
+      <c r="C124" s="24"/>
+      <c r="D124" s="25"/>
       <c r="E124" s="18"/>
       <c r="F124" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G124" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H124" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I124" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J124" s="20"/>
       <c r="K124" s="2"/>
       <c r="L124" s="2"/>
       <c r="M124" s="18"/>
       <c r="N124" s="18"/>
-      <c r="O124" s="57"/>
-      <c r="P124" s="58"/>
+      <c r="O124" s="24"/>
+      <c r="P124" s="25"/>
       <c r="Q124" s="3"/>
     </row>
     <row r="125" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="59"/>
-      <c r="B125" s="60"/>
-      <c r="C125" s="59"/>
-      <c r="D125" s="60"/>
+      <c r="A125" s="26"/>
+      <c r="B125" s="27"/>
+      <c r="C125" s="26"/>
+      <c r="D125" s="27"/>
       <c r="E125" s="21"/>
       <c r="F125" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G125" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H125" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I125" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J125" s="22"/>
       <c r="K125" s="23"/>
       <c r="L125" s="23"/>
       <c r="M125" s="21"/>
       <c r="N125" s="21"/>
-      <c r="O125" s="59"/>
-      <c r="P125" s="60"/>
+      <c r="O125" s="26"/>
+      <c r="P125" s="27"/>
       <c r="Q125" s="23"/>
     </row>
     <row r="126" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="57"/>
-      <c r="B126" s="58"/>
-      <c r="C126" s="57"/>
-      <c r="D126" s="58"/>
+      <c r="A126" s="24"/>
+      <c r="B126" s="25"/>
+      <c r="C126" s="24"/>
+      <c r="D126" s="25"/>
       <c r="E126" s="18"/>
       <c r="F126" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G126" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H126" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I126" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J126" s="20"/>
       <c r="K126" s="2"/>
       <c r="L126" s="2"/>
       <c r="M126" s="18"/>
       <c r="N126" s="18"/>
-      <c r="O126" s="57"/>
-      <c r="P126" s="58"/>
+      <c r="O126" s="24"/>
+      <c r="P126" s="25"/>
       <c r="Q126" s="3"/>
     </row>
     <row r="127" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="59"/>
-      <c r="B127" s="60"/>
-      <c r="C127" s="59"/>
-      <c r="D127" s="60"/>
+      <c r="A127" s="26"/>
+      <c r="B127" s="27"/>
+      <c r="C127" s="26"/>
+      <c r="D127" s="27"/>
       <c r="E127" s="21"/>
       <c r="F127" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G127" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H127" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I127" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J127" s="22"/>
       <c r="K127" s="23"/>
       <c r="L127" s="23"/>
       <c r="M127" s="21"/>
       <c r="N127" s="21"/>
-      <c r="O127" s="59"/>
-      <c r="P127" s="60"/>
+      <c r="O127" s="26"/>
+      <c r="P127" s="27"/>
       <c r="Q127" s="23"/>
     </row>
     <row r="128" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="57"/>
-      <c r="B128" s="58"/>
-      <c r="C128" s="57"/>
-      <c r="D128" s="58"/>
+      <c r="A128" s="24"/>
+      <c r="B128" s="25"/>
+      <c r="C128" s="24"/>
+      <c r="D128" s="25"/>
       <c r="E128" s="18"/>
       <c r="F128" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G128" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H128" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I128" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J128" s="20"/>
       <c r="K128" s="2"/>
       <c r="L128" s="2"/>
       <c r="M128" s="18"/>
       <c r="N128" s="18"/>
-      <c r="O128" s="57"/>
-      <c r="P128" s="58"/>
+      <c r="O128" s="24"/>
+      <c r="P128" s="25"/>
       <c r="Q128" s="3"/>
     </row>
     <row r="129" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="59"/>
-      <c r="B129" s="60"/>
-      <c r="C129" s="59"/>
-      <c r="D129" s="60"/>
+      <c r="A129" s="26"/>
+      <c r="B129" s="27"/>
+      <c r="C129" s="26"/>
+      <c r="D129" s="27"/>
       <c r="E129" s="21"/>
       <c r="F129" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G129" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H129" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I129" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J129" s="22"/>
       <c r="K129" s="23"/>
       <c r="L129" s="23"/>
       <c r="M129" s="21"/>
       <c r="N129" s="21"/>
-      <c r="O129" s="59"/>
-      <c r="P129" s="60"/>
+      <c r="O129" s="26"/>
+      <c r="P129" s="27"/>
       <c r="Q129" s="23"/>
     </row>
     <row r="130" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="57"/>
-      <c r="B130" s="58"/>
-      <c r="C130" s="57"/>
-      <c r="D130" s="58"/>
+      <c r="A130" s="24"/>
+      <c r="B130" s="25"/>
+      <c r="C130" s="24"/>
+      <c r="D130" s="25"/>
       <c r="E130" s="18"/>
       <c r="F130" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G130" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H130" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I130" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J130" s="20"/>
       <c r="K130" s="2"/>
       <c r="L130" s="2"/>
       <c r="M130" s="18"/>
       <c r="N130" s="18"/>
-      <c r="O130" s="57"/>
-      <c r="P130" s="58"/>
+      <c r="O130" s="24"/>
+      <c r="P130" s="25"/>
       <c r="Q130" s="3"/>
     </row>
     <row r="131" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="59"/>
-      <c r="B131" s="60"/>
-      <c r="C131" s="59"/>
-      <c r="D131" s="60"/>
+      <c r="A131" s="26"/>
+      <c r="B131" s="27"/>
+      <c r="C131" s="26"/>
+      <c r="D131" s="27"/>
       <c r="E131" s="21"/>
       <c r="F131" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G131" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H131" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I131" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J131" s="22"/>
       <c r="K131" s="23"/>
       <c r="L131" s="23"/>
       <c r="M131" s="21"/>
       <c r="N131" s="21"/>
-      <c r="O131" s="59"/>
-      <c r="P131" s="60"/>
+      <c r="O131" s="26"/>
+      <c r="P131" s="27"/>
       <c r="Q131" s="23"/>
     </row>
     <row r="132" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="57"/>
-      <c r="B132" s="58"/>
-      <c r="C132" s="57"/>
-      <c r="D132" s="58"/>
+      <c r="A132" s="24"/>
+      <c r="B132" s="25"/>
+      <c r="C132" s="24"/>
+      <c r="D132" s="25"/>
       <c r="E132" s="18"/>
       <c r="F132" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G132" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H132" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I132" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J132" s="20"/>
       <c r="K132" s="2"/>
       <c r="L132" s="2"/>
       <c r="M132" s="18"/>
       <c r="N132" s="18"/>
-      <c r="O132" s="57"/>
-      <c r="P132" s="58"/>
+      <c r="O132" s="24"/>
+      <c r="P132" s="25"/>
       <c r="Q132" s="3"/>
     </row>
     <row r="133" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="59"/>
-      <c r="B133" s="60"/>
-      <c r="C133" s="59"/>
-      <c r="D133" s="60"/>
+      <c r="A133" s="26"/>
+      <c r="B133" s="27"/>
+      <c r="C133" s="26"/>
+      <c r="D133" s="27"/>
       <c r="E133" s="21"/>
       <c r="F133" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G133" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H133" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I133" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J133" s="22"/>
       <c r="K133" s="23"/>
       <c r="L133" s="23"/>
       <c r="M133" s="21"/>
       <c r="N133" s="21"/>
-      <c r="O133" s="59"/>
-      <c r="P133" s="60"/>
+      <c r="O133" s="26"/>
+      <c r="P133" s="27"/>
       <c r="Q133" s="23"/>
     </row>
     <row r="134" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="57"/>
-      <c r="B134" s="58"/>
-      <c r="C134" s="57"/>
-      <c r="D134" s="58"/>
+      <c r="A134" s="24"/>
+      <c r="B134" s="25"/>
+      <c r="C134" s="24"/>
+      <c r="D134" s="25"/>
       <c r="E134" s="18"/>
       <c r="F134" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G134" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H134" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I134" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J134" s="20"/>
       <c r="K134" s="2"/>
       <c r="L134" s="2"/>
       <c r="M134" s="18"/>
       <c r="N134" s="18"/>
-      <c r="O134" s="57"/>
-      <c r="P134" s="58"/>
+      <c r="O134" s="24"/>
+      <c r="P134" s="25"/>
       <c r="Q134" s="3"/>
     </row>
     <row r="135" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="59"/>
-      <c r="B135" s="60"/>
-      <c r="C135" s="59"/>
-      <c r="D135" s="60"/>
+      <c r="A135" s="26"/>
+      <c r="B135" s="27"/>
+      <c r="C135" s="26"/>
+      <c r="D135" s="27"/>
       <c r="E135" s="21"/>
       <c r="F135" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G135" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H135" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I135" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J135" s="22"/>
       <c r="K135" s="23"/>
       <c r="L135" s="23"/>
       <c r="M135" s="21"/>
       <c r="N135" s="21"/>
-      <c r="O135" s="59"/>
-      <c r="P135" s="60"/>
+      <c r="O135" s="26"/>
+      <c r="P135" s="27"/>
       <c r="Q135" s="23"/>
     </row>
     <row r="136" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="57"/>
-      <c r="B136" s="58"/>
-      <c r="C136" s="57"/>
-      <c r="D136" s="58"/>
+      <c r="A136" s="24"/>
+      <c r="B136" s="25"/>
+      <c r="C136" s="24"/>
+      <c r="D136" s="25"/>
       <c r="E136" s="18"/>
       <c r="F136" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G136" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H136" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I136" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J136" s="20"/>
       <c r="K136" s="2"/>
       <c r="L136" s="2"/>
       <c r="M136" s="18"/>
       <c r="N136" s="18"/>
-      <c r="O136" s="57"/>
-      <c r="P136" s="58"/>
+      <c r="O136" s="24"/>
+      <c r="P136" s="25"/>
       <c r="Q136" s="3"/>
     </row>
     <row r="137" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="59"/>
-      <c r="B137" s="60"/>
-      <c r="C137" s="59"/>
-      <c r="D137" s="60"/>
+      <c r="A137" s="26"/>
+      <c r="B137" s="27"/>
+      <c r="C137" s="26"/>
+      <c r="D137" s="27"/>
       <c r="E137" s="21"/>
       <c r="F137" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G137" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H137" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I137" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J137" s="22"/>
       <c r="K137" s="23"/>
       <c r="L137" s="23"/>
       <c r="M137" s="21"/>
       <c r="N137" s="21"/>
-      <c r="O137" s="59"/>
-      <c r="P137" s="60"/>
+      <c r="O137" s="26"/>
+      <c r="P137" s="27"/>
       <c r="Q137" s="23"/>
     </row>
     <row r="138" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="57"/>
-      <c r="B138" s="58"/>
-      <c r="C138" s="57"/>
-      <c r="D138" s="58"/>
+      <c r="A138" s="24"/>
+      <c r="B138" s="25"/>
+      <c r="C138" s="24"/>
+      <c r="D138" s="25"/>
       <c r="E138" s="18"/>
       <c r="F138" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G138" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H138" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I138" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J138" s="20"/>
       <c r="K138" s="2"/>
       <c r="L138" s="2"/>
       <c r="M138" s="18"/>
       <c r="N138" s="18"/>
-      <c r="O138" s="57"/>
-      <c r="P138" s="58"/>
+      <c r="O138" s="24"/>
+      <c r="P138" s="25"/>
       <c r="Q138" s="3"/>
     </row>
     <row r="139" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="59"/>
-      <c r="B139" s="60"/>
-      <c r="C139" s="59"/>
-      <c r="D139" s="60"/>
+      <c r="A139" s="26"/>
+      <c r="B139" s="27"/>
+      <c r="C139" s="26"/>
+      <c r="D139" s="27"/>
       <c r="E139" s="21"/>
       <c r="F139" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G139" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H139" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I139" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J139" s="22"/>
       <c r="K139" s="23"/>
       <c r="L139" s="23"/>
       <c r="M139" s="21"/>
       <c r="N139" s="21"/>
-      <c r="O139" s="59"/>
-      <c r="P139" s="60"/>
+      <c r="O139" s="26"/>
+      <c r="P139" s="27"/>
       <c r="Q139" s="23"/>
     </row>
     <row r="140" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="57"/>
-      <c r="B140" s="58"/>
-      <c r="C140" s="57"/>
-      <c r="D140" s="58"/>
+      <c r="A140" s="24"/>
+      <c r="B140" s="25"/>
+      <c r="C140" s="24"/>
+      <c r="D140" s="25"/>
       <c r="E140" s="18"/>
       <c r="F140" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G140" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H140" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I140" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J140" s="20"/>
       <c r="K140" s="2"/>
       <c r="L140" s="2"/>
       <c r="M140" s="18"/>
       <c r="N140" s="18"/>
-      <c r="O140" s="57"/>
-      <c r="P140" s="58"/>
+      <c r="O140" s="24"/>
+      <c r="P140" s="25"/>
       <c r="Q140" s="3"/>
     </row>
     <row r="141" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="59"/>
-      <c r="B141" s="60"/>
-      <c r="C141" s="59"/>
-      <c r="D141" s="60"/>
+      <c r="A141" s="26"/>
+      <c r="B141" s="27"/>
+      <c r="C141" s="26"/>
+      <c r="D141" s="27"/>
       <c r="E141" s="21"/>
       <c r="F141" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G141" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H141" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I141" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J141" s="22"/>
       <c r="K141" s="23"/>
       <c r="L141" s="23"/>
       <c r="M141" s="21"/>
       <c r="N141" s="21"/>
-      <c r="O141" s="59"/>
-      <c r="P141" s="60"/>
+      <c r="O141" s="26"/>
+      <c r="P141" s="27"/>
       <c r="Q141" s="23"/>
     </row>
     <row r="142" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="57"/>
-      <c r="B142" s="58"/>
-      <c r="C142" s="57"/>
-      <c r="D142" s="58"/>
+      <c r="A142" s="24"/>
+      <c r="B142" s="25"/>
+      <c r="C142" s="24"/>
+      <c r="D142" s="25"/>
       <c r="E142" s="18"/>
       <c r="F142" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G142" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H142" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I142" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J142" s="20"/>
       <c r="K142" s="2"/>
       <c r="L142" s="2"/>
       <c r="M142" s="18"/>
       <c r="N142" s="18"/>
-      <c r="O142" s="57"/>
-      <c r="P142" s="58"/>
+      <c r="O142" s="24"/>
+      <c r="P142" s="25"/>
       <c r="Q142" s="3"/>
     </row>
     <row r="143" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A143" s="59"/>
-      <c r="B143" s="60"/>
-      <c r="C143" s="59"/>
-      <c r="D143" s="60"/>
+      <c r="A143" s="26"/>
+      <c r="B143" s="27"/>
+      <c r="C143" s="26"/>
+      <c r="D143" s="27"/>
       <c r="E143" s="21"/>
       <c r="F143" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G143" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H143" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I143" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J143" s="22"/>
       <c r="K143" s="23"/>
       <c r="L143" s="23"/>
       <c r="M143" s="21"/>
       <c r="N143" s="21"/>
-      <c r="O143" s="59"/>
-      <c r="P143" s="60"/>
+      <c r="O143" s="26"/>
+      <c r="P143" s="27"/>
       <c r="Q143" s="23"/>
     </row>
     <row r="144" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="57"/>
-      <c r="B144" s="58"/>
-      <c r="C144" s="57"/>
-      <c r="D144" s="58"/>
+      <c r="A144" s="24"/>
+      <c r="B144" s="25"/>
+      <c r="C144" s="24"/>
+      <c r="D144" s="25"/>
       <c r="E144" s="18"/>
       <c r="F144" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G144" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H144" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I144" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J144" s="20"/>
       <c r="K144" s="2"/>
       <c r="L144" s="2"/>
       <c r="M144" s="18"/>
       <c r="N144" s="18"/>
-      <c r="O144" s="57"/>
-      <c r="P144" s="58"/>
+      <c r="O144" s="24"/>
+      <c r="P144" s="25"/>
       <c r="Q144" s="3"/>
     </row>
     <row r="145" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="59"/>
-      <c r="B145" s="60"/>
-      <c r="C145" s="59"/>
-      <c r="D145" s="60"/>
+      <c r="A145" s="26"/>
+      <c r="B145" s="27"/>
+      <c r="C145" s="26"/>
+      <c r="D145" s="27"/>
       <c r="E145" s="21"/>
       <c r="F145" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G145" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H145" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I145" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J145" s="22"/>
       <c r="K145" s="23"/>
       <c r="L145" s="23"/>
       <c r="M145" s="21"/>
       <c r="N145" s="21"/>
-      <c r="O145" s="59"/>
-      <c r="P145" s="60"/>
+      <c r="O145" s="26"/>
+      <c r="P145" s="27"/>
       <c r="Q145" s="23"/>
     </row>
     <row r="146" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="57"/>
-      <c r="B146" s="58"/>
-      <c r="C146" s="57"/>
-      <c r="D146" s="58"/>
+      <c r="A146" s="24"/>
+      <c r="B146" s="25"/>
+      <c r="C146" s="24"/>
+      <c r="D146" s="25"/>
       <c r="E146" s="18"/>
       <c r="F146" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G146" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H146" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I146" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J146" s="20"/>
       <c r="K146" s="2"/>
       <c r="L146" s="2"/>
       <c r="M146" s="18"/>
       <c r="N146" s="18"/>
-      <c r="O146" s="57"/>
-      <c r="P146" s="58"/>
+      <c r="O146" s="24"/>
+      <c r="P146" s="25"/>
       <c r="Q146" s="3"/>
     </row>
     <row r="147" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="59"/>
-      <c r="B147" s="60"/>
-      <c r="C147" s="59"/>
-      <c r="D147" s="60"/>
+      <c r="A147" s="26"/>
+      <c r="B147" s="27"/>
+      <c r="C147" s="26"/>
+      <c r="D147" s="27"/>
       <c r="E147" s="21"/>
       <c r="F147" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G147" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H147" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I147" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J147" s="22"/>
       <c r="K147" s="23"/>
       <c r="L147" s="23"/>
       <c r="M147" s="21"/>
       <c r="N147" s="21"/>
-      <c r="O147" s="59"/>
-      <c r="P147" s="60"/>
+      <c r="O147" s="26"/>
+      <c r="P147" s="27"/>
       <c r="Q147" s="23"/>
     </row>
     <row r="148" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="57"/>
-      <c r="B148" s="58"/>
-      <c r="C148" s="57"/>
-      <c r="D148" s="58"/>
+      <c r="A148" s="24"/>
+      <c r="B148" s="25"/>
+      <c r="C148" s="24"/>
+      <c r="D148" s="25"/>
       <c r="E148" s="18"/>
       <c r="F148" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G148" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H148" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I148" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J148" s="20"/>
       <c r="K148" s="2"/>
       <c r="L148" s="2"/>
       <c r="M148" s="18"/>
       <c r="N148" s="18"/>
-      <c r="O148" s="57"/>
-      <c r="P148" s="58"/>
+      <c r="O148" s="24"/>
+      <c r="P148" s="25"/>
       <c r="Q148" s="3"/>
     </row>
     <row r="149" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="59"/>
-      <c r="B149" s="60"/>
-      <c r="C149" s="59"/>
-      <c r="D149" s="60"/>
+      <c r="A149" s="26"/>
+      <c r="B149" s="27"/>
+      <c r="C149" s="26"/>
+      <c r="D149" s="27"/>
       <c r="E149" s="21"/>
       <c r="F149" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G149" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H149" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I149" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J149" s="22"/>
       <c r="K149" s="23"/>
       <c r="L149" s="23"/>
       <c r="M149" s="21"/>
       <c r="N149" s="21"/>
-      <c r="O149" s="59"/>
-      <c r="P149" s="60"/>
+      <c r="O149" s="26"/>
+      <c r="P149" s="27"/>
       <c r="Q149" s="23"/>
     </row>
     <row r="150" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="57"/>
-      <c r="B150" s="58"/>
-      <c r="C150" s="57"/>
-      <c r="D150" s="58"/>
+      <c r="A150" s="24"/>
+      <c r="B150" s="25"/>
+      <c r="C150" s="24"/>
+      <c r="D150" s="25"/>
       <c r="E150" s="18"/>
       <c r="F150" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G150" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H150" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I150" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J150" s="20"/>
       <c r="K150" s="2"/>
       <c r="L150" s="2"/>
       <c r="M150" s="18"/>
       <c r="N150" s="18"/>
-      <c r="O150" s="57"/>
-      <c r="P150" s="58"/>
+      <c r="O150" s="24"/>
+      <c r="P150" s="25"/>
       <c r="Q150" s="3"/>
     </row>
     <row r="151" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A151" s="59"/>
-      <c r="B151" s="60"/>
-      <c r="C151" s="59"/>
-      <c r="D151" s="60"/>
+      <c r="A151" s="26"/>
+      <c r="B151" s="27"/>
+      <c r="C151" s="26"/>
+      <c r="D151" s="27"/>
       <c r="E151" s="21"/>
       <c r="F151" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G151" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H151" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I151" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J151" s="22"/>
       <c r="K151" s="23"/>
       <c r="L151" s="23"/>
       <c r="M151" s="21"/>
       <c r="N151" s="21"/>
-      <c r="O151" s="59"/>
-      <c r="P151" s="60"/>
+      <c r="O151" s="26"/>
+      <c r="P151" s="27"/>
       <c r="Q151" s="23"/>
     </row>
     <row r="152" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="57"/>
-      <c r="B152" s="58"/>
-      <c r="C152" s="57"/>
-      <c r="D152" s="58"/>
+      <c r="A152" s="24"/>
+      <c r="B152" s="25"/>
+      <c r="C152" s="24"/>
+      <c r="D152" s="25"/>
       <c r="E152" s="18"/>
       <c r="F152" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G152" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H152" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I152" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J152" s="20"/>
       <c r="K152" s="2"/>
       <c r="L152" s="2"/>
       <c r="M152" s="18"/>
       <c r="N152" s="18"/>
-      <c r="O152" s="57"/>
-      <c r="P152" s="58"/>
+      <c r="O152" s="24"/>
+      <c r="P152" s="25"/>
       <c r="Q152" s="3"/>
     </row>
     <row r="153" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="59"/>
-      <c r="B153" s="60"/>
-      <c r="C153" s="59"/>
-      <c r="D153" s="60"/>
+      <c r="A153" s="26"/>
+      <c r="B153" s="27"/>
+      <c r="C153" s="26"/>
+      <c r="D153" s="27"/>
       <c r="E153" s="21"/>
       <c r="F153" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G153" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H153" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I153" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J153" s="22"/>
       <c r="K153" s="23"/>
       <c r="L153" s="23"/>
       <c r="M153" s="21"/>
       <c r="N153" s="21"/>
-      <c r="O153" s="59"/>
-      <c r="P153" s="60"/>
+      <c r="O153" s="26"/>
+      <c r="P153" s="27"/>
       <c r="Q153" s="23"/>
     </row>
     <row r="154" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="57"/>
-      <c r="B154" s="58"/>
-      <c r="C154" s="57"/>
-      <c r="D154" s="58"/>
+      <c r="A154" s="24"/>
+      <c r="B154" s="25"/>
+      <c r="C154" s="24"/>
+      <c r="D154" s="25"/>
       <c r="E154" s="18"/>
       <c r="F154" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G154" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H154" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I154" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J154" s="20"/>
       <c r="K154" s="2"/>
       <c r="L154" s="2"/>
       <c r="M154" s="18"/>
       <c r="N154" s="18"/>
-      <c r="O154" s="57"/>
-      <c r="P154" s="58"/>
+      <c r="O154" s="24"/>
+      <c r="P154" s="25"/>
       <c r="Q154" s="3"/>
     </row>
     <row r="155" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A155" s="59"/>
-      <c r="B155" s="60"/>
-      <c r="C155" s="59"/>
-      <c r="D155" s="60"/>
+      <c r="A155" s="26"/>
+      <c r="B155" s="27"/>
+      <c r="C155" s="26"/>
+      <c r="D155" s="27"/>
       <c r="E155" s="21"/>
       <c r="F155" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G155" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H155" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I155" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J155" s="22"/>
       <c r="K155" s="23"/>
       <c r="L155" s="23"/>
       <c r="M155" s="21"/>
       <c r="N155" s="21"/>
-      <c r="O155" s="59"/>
-      <c r="P155" s="60"/>
+      <c r="O155" s="26"/>
+      <c r="P155" s="27"/>
       <c r="Q155" s="23"/>
     </row>
     <row r="156" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="57"/>
-      <c r="B156" s="58"/>
-      <c r="C156" s="57"/>
-      <c r="D156" s="58"/>
+      <c r="A156" s="24"/>
+      <c r="B156" s="25"/>
+      <c r="C156" s="24"/>
+      <c r="D156" s="25"/>
       <c r="E156" s="18"/>
       <c r="F156" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G156" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H156" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I156" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J156" s="20"/>
       <c r="K156" s="2"/>
       <c r="L156" s="2"/>
       <c r="M156" s="18"/>
       <c r="N156" s="18"/>
-      <c r="O156" s="57"/>
-      <c r="P156" s="58"/>
+      <c r="O156" s="24"/>
+      <c r="P156" s="25"/>
       <c r="Q156" s="3"/>
     </row>
     <row r="157" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="59"/>
-      <c r="B157" s="60"/>
-      <c r="C157" s="59"/>
-      <c r="D157" s="60"/>
+      <c r="A157" s="26"/>
+      <c r="B157" s="27"/>
+      <c r="C157" s="26"/>
+      <c r="D157" s="27"/>
       <c r="E157" s="21"/>
       <c r="F157" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G157" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H157" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I157" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J157" s="22"/>
       <c r="K157" s="23"/>
       <c r="L157" s="23"/>
       <c r="M157" s="21"/>
       <c r="N157" s="21"/>
-      <c r="O157" s="59"/>
-      <c r="P157" s="60"/>
+      <c r="O157" s="26"/>
+      <c r="P157" s="27"/>
       <c r="Q157" s="23"/>
     </row>
     <row r="158" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="57"/>
-      <c r="B158" s="58"/>
-      <c r="C158" s="57"/>
-      <c r="D158" s="58"/>
+      <c r="A158" s="24"/>
+      <c r="B158" s="25"/>
+      <c r="C158" s="24"/>
+      <c r="D158" s="25"/>
       <c r="E158" s="18"/>
       <c r="F158" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G158" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H158" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I158" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J158" s="20"/>
       <c r="K158" s="2"/>
       <c r="L158" s="2"/>
       <c r="M158" s="18"/>
       <c r="N158" s="18"/>
-      <c r="O158" s="57"/>
-      <c r="P158" s="58"/>
+      <c r="O158" s="24"/>
+      <c r="P158" s="25"/>
       <c r="Q158" s="3"/>
     </row>
     <row r="159" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="59"/>
-      <c r="B159" s="60"/>
-      <c r="C159" s="59"/>
-      <c r="D159" s="60"/>
+      <c r="A159" s="26"/>
+      <c r="B159" s="27"/>
+      <c r="C159" s="26"/>
+      <c r="D159" s="27"/>
       <c r="E159" s="21"/>
       <c r="F159" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G159" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H159" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I159" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J159" s="22"/>
       <c r="K159" s="23"/>
       <c r="L159" s="23"/>
       <c r="M159" s="21"/>
       <c r="N159" s="21"/>
-      <c r="O159" s="59"/>
-      <c r="P159" s="60"/>
+      <c r="O159" s="26"/>
+      <c r="P159" s="27"/>
       <c r="Q159" s="23"/>
     </row>
     <row r="160" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="57"/>
-      <c r="B160" s="58"/>
-      <c r="C160" s="57"/>
-      <c r="D160" s="58"/>
+      <c r="A160" s="24"/>
+      <c r="B160" s="25"/>
+      <c r="C160" s="24"/>
+      <c r="D160" s="25"/>
       <c r="E160" s="18"/>
       <c r="F160" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G160" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H160" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I160" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J160" s="20"/>
       <c r="K160" s="2"/>
       <c r="L160" s="2"/>
       <c r="M160" s="18"/>
       <c r="N160" s="18"/>
-      <c r="O160" s="57"/>
-      <c r="P160" s="58"/>
+      <c r="O160" s="24"/>
+      <c r="P160" s="25"/>
       <c r="Q160" s="3"/>
     </row>
     <row r="161" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A161" s="59"/>
-      <c r="B161" s="60"/>
-      <c r="C161" s="59"/>
-      <c r="D161" s="60"/>
+      <c r="A161" s="26"/>
+      <c r="B161" s="27"/>
+      <c r="C161" s="26"/>
+      <c r="D161" s="27"/>
       <c r="E161" s="21"/>
       <c r="F161" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G161" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H161" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I161" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J161" s="22"/>
       <c r="K161" s="23"/>
       <c r="L161" s="23"/>
       <c r="M161" s="21"/>
       <c r="N161" s="21"/>
-      <c r="O161" s="59"/>
-      <c r="P161" s="60"/>
+      <c r="O161" s="26"/>
+      <c r="P161" s="27"/>
       <c r="Q161" s="23"/>
     </row>
     <row r="162" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="57"/>
-      <c r="B162" s="58"/>
-      <c r="C162" s="57"/>
-      <c r="D162" s="58"/>
+      <c r="A162" s="24"/>
+      <c r="B162" s="25"/>
+      <c r="C162" s="24"/>
+      <c r="D162" s="25"/>
       <c r="E162" s="18"/>
       <c r="F162" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G162" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H162" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I162" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J162" s="20"/>
       <c r="K162" s="2"/>
       <c r="L162" s="2"/>
       <c r="M162" s="18"/>
       <c r="N162" s="18"/>
-      <c r="O162" s="57"/>
-      <c r="P162" s="58"/>
+      <c r="O162" s="24"/>
+      <c r="P162" s="25"/>
       <c r="Q162" s="3"/>
     </row>
     <row r="163" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A163" s="59"/>
-      <c r="B163" s="60"/>
-      <c r="C163" s="59"/>
-      <c r="D163" s="60"/>
+      <c r="A163" s="26"/>
+      <c r="B163" s="27"/>
+      <c r="C163" s="26"/>
+      <c r="D163" s="27"/>
       <c r="E163" s="21"/>
       <c r="F163" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G163" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H163" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I163" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J163" s="22"/>
       <c r="K163" s="23"/>
       <c r="L163" s="23"/>
       <c r="M163" s="21"/>
       <c r="N163" s="21"/>
-      <c r="O163" s="59"/>
-      <c r="P163" s="60"/>
+      <c r="O163" s="26"/>
+      <c r="P163" s="27"/>
       <c r="Q163" s="23"/>
     </row>
     <row r="164" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="57"/>
-      <c r="B164" s="58"/>
-      <c r="C164" s="57"/>
-      <c r="D164" s="58"/>
+      <c r="A164" s="24"/>
+      <c r="B164" s="25"/>
+      <c r="C164" s="24"/>
+      <c r="D164" s="25"/>
       <c r="E164" s="18"/>
       <c r="F164" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G164" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H164" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I164" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J164" s="20"/>
       <c r="K164" s="2"/>
       <c r="L164" s="2"/>
       <c r="M164" s="18"/>
       <c r="N164" s="18"/>
-      <c r="O164" s="57"/>
-      <c r="P164" s="58"/>
+      <c r="O164" s="24"/>
+      <c r="P164" s="25"/>
       <c r="Q164" s="3"/>
     </row>
     <row r="165" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A165" s="59"/>
-      <c r="B165" s="60"/>
-      <c r="C165" s="59"/>
-      <c r="D165" s="60"/>
+      <c r="A165" s="26"/>
+      <c r="B165" s="27"/>
+      <c r="C165" s="26"/>
+      <c r="D165" s="27"/>
       <c r="E165" s="21"/>
       <c r="F165" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G165" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H165" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I165" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J165" s="22"/>
       <c r="K165" s="23"/>
       <c r="L165" s="23"/>
       <c r="M165" s="21"/>
       <c r="N165" s="21"/>
-      <c r="O165" s="59"/>
-      <c r="P165" s="60"/>
+      <c r="O165" s="26"/>
+      <c r="P165" s="27"/>
       <c r="Q165" s="23"/>
     </row>
     <row r="166" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="57"/>
-      <c r="B166" s="58"/>
-      <c r="C166" s="57"/>
-      <c r="D166" s="58"/>
+      <c r="A166" s="24"/>
+      <c r="B166" s="25"/>
+      <c r="C166" s="24"/>
+      <c r="D166" s="25"/>
       <c r="E166" s="18"/>
       <c r="F166" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G166" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H166" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I166" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J166" s="20"/>
       <c r="K166" s="2"/>
       <c r="L166" s="2"/>
       <c r="M166" s="18"/>
       <c r="N166" s="18"/>
-      <c r="O166" s="57"/>
-      <c r="P166" s="58"/>
+      <c r="O166" s="24"/>
+      <c r="P166" s="25"/>
       <c r="Q166" s="3"/>
     </row>
     <row r="167" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A167" s="59"/>
-      <c r="B167" s="60"/>
-      <c r="C167" s="59"/>
-      <c r="D167" s="60"/>
+      <c r="A167" s="26"/>
+      <c r="B167" s="27"/>
+      <c r="C167" s="26"/>
+      <c r="D167" s="27"/>
       <c r="E167" s="21"/>
       <c r="F167" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G167" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H167" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I167" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J167" s="22"/>
       <c r="K167" s="23"/>
       <c r="L167" s="23"/>
       <c r="M167" s="21"/>
       <c r="N167" s="21"/>
-      <c r="O167" s="59"/>
-      <c r="P167" s="60"/>
+      <c r="O167" s="26"/>
+      <c r="P167" s="27"/>
       <c r="Q167" s="23"/>
     </row>
     <row r="168" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="57"/>
-      <c r="B168" s="58"/>
-      <c r="C168" s="57"/>
-      <c r="D168" s="58"/>
+      <c r="A168" s="24"/>
+      <c r="B168" s="25"/>
+      <c r="C168" s="24"/>
+      <c r="D168" s="25"/>
       <c r="E168" s="18"/>
       <c r="F168" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G168" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H168" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I168" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J168" s="20"/>
       <c r="K168" s="2"/>
       <c r="L168" s="2"/>
       <c r="M168" s="18"/>
       <c r="N168" s="18"/>
-      <c r="O168" s="57"/>
-      <c r="P168" s="58"/>
+      <c r="O168" s="24"/>
+      <c r="P168" s="25"/>
       <c r="Q168" s="3"/>
     </row>
     <row r="169" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="59"/>
-      <c r="B169" s="60"/>
-      <c r="C169" s="59"/>
-      <c r="D169" s="60"/>
+      <c r="A169" s="26"/>
+      <c r="B169" s="27"/>
+      <c r="C169" s="26"/>
+      <c r="D169" s="27"/>
       <c r="E169" s="21"/>
       <c r="F169" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G169" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H169" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I169" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J169" s="22"/>
       <c r="K169" s="23"/>
       <c r="L169" s="23"/>
       <c r="M169" s="21"/>
       <c r="N169" s="21"/>
-      <c r="O169" s="59"/>
-      <c r="P169" s="60"/>
+      <c r="O169" s="26"/>
+      <c r="P169" s="27"/>
       <c r="Q169" s="23"/>
     </row>
     <row r="170" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="57"/>
-      <c r="B170" s="58"/>
-      <c r="C170" s="57"/>
-      <c r="D170" s="58"/>
+      <c r="A170" s="24"/>
+      <c r="B170" s="25"/>
+      <c r="C170" s="24"/>
+      <c r="D170" s="25"/>
       <c r="E170" s="18"/>
       <c r="F170" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G170" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H170" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I170" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J170" s="20"/>
       <c r="K170" s="2"/>
       <c r="L170" s="2"/>
       <c r="M170" s="18"/>
       <c r="N170" s="18"/>
-      <c r="O170" s="57"/>
-      <c r="P170" s="58"/>
+      <c r="O170" s="24"/>
+      <c r="P170" s="25"/>
       <c r="Q170" s="3"/>
     </row>
     <row r="171" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A171" s="59"/>
-      <c r="B171" s="60"/>
-      <c r="C171" s="59"/>
-      <c r="D171" s="60"/>
+      <c r="A171" s="26"/>
+      <c r="B171" s="27"/>
+      <c r="C171" s="26"/>
+      <c r="D171" s="27"/>
       <c r="E171" s="21"/>
       <c r="F171" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G171" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H171" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I171" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J171" s="22"/>
       <c r="K171" s="23"/>
       <c r="L171" s="23"/>
       <c r="M171" s="21"/>
       <c r="N171" s="21"/>
-      <c r="O171" s="59"/>
-      <c r="P171" s="60"/>
+      <c r="O171" s="26"/>
+      <c r="P171" s="27"/>
       <c r="Q171" s="23"/>
     </row>
     <row r="172" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="57"/>
-      <c r="B172" s="58"/>
-      <c r="C172" s="57"/>
-      <c r="D172" s="58"/>
+      <c r="A172" s="24"/>
+      <c r="B172" s="25"/>
+      <c r="C172" s="24"/>
+      <c r="D172" s="25"/>
       <c r="E172" s="18"/>
       <c r="F172" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G172" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H172" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I172" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J172" s="20"/>
       <c r="K172" s="2"/>
       <c r="L172" s="2"/>
       <c r="M172" s="18"/>
       <c r="N172" s="18"/>
-      <c r="O172" s="57"/>
-      <c r="P172" s="58"/>
+      <c r="O172" s="24"/>
+      <c r="P172" s="25"/>
       <c r="Q172" s="3"/>
     </row>
     <row r="173" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="59"/>
-      <c r="B173" s="60"/>
-      <c r="C173" s="59"/>
-      <c r="D173" s="60"/>
+      <c r="A173" s="26"/>
+      <c r="B173" s="27"/>
+      <c r="C173" s="26"/>
+      <c r="D173" s="27"/>
       <c r="E173" s="21"/>
       <c r="F173" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G173" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H173" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I173" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J173" s="22"/>
       <c r="K173" s="23"/>
       <c r="L173" s="23"/>
       <c r="M173" s="21"/>
       <c r="N173" s="21"/>
-      <c r="O173" s="59"/>
-      <c r="P173" s="60"/>
+      <c r="O173" s="26"/>
+      <c r="P173" s="27"/>
       <c r="Q173" s="23"/>
     </row>
     <row r="174" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="57"/>
-      <c r="B174" s="58"/>
-      <c r="C174" s="57"/>
-      <c r="D174" s="58"/>
+      <c r="A174" s="24"/>
+      <c r="B174" s="25"/>
+      <c r="C174" s="24"/>
+      <c r="D174" s="25"/>
       <c r="E174" s="18"/>
       <c r="F174" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G174" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H174" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I174" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J174" s="20"/>
       <c r="K174" s="2"/>
       <c r="L174" s="2"/>
       <c r="M174" s="18"/>
       <c r="N174" s="18"/>
-      <c r="O174" s="57"/>
-      <c r="P174" s="58"/>
+      <c r="O174" s="24"/>
+      <c r="P174" s="25"/>
       <c r="Q174" s="3"/>
     </row>
     <row r="175" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A175" s="59"/>
-      <c r="B175" s="60"/>
-      <c r="C175" s="59"/>
-      <c r="D175" s="60"/>
+      <c r="A175" s="26"/>
+      <c r="B175" s="27"/>
+      <c r="C175" s="26"/>
+      <c r="D175" s="27"/>
       <c r="E175" s="21"/>
       <c r="F175" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G175" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H175" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I175" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J175" s="22"/>
       <c r="K175" s="23"/>
       <c r="L175" s="23"/>
       <c r="M175" s="21"/>
       <c r="N175" s="21"/>
-      <c r="O175" s="59"/>
-      <c r="P175" s="60"/>
+      <c r="O175" s="26"/>
+      <c r="P175" s="27"/>
       <c r="Q175" s="23"/>
     </row>
     <row r="176" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="57"/>
-      <c r="B176" s="58"/>
-      <c r="C176" s="57"/>
-      <c r="D176" s="58"/>
+      <c r="A176" s="24"/>
+      <c r="B176" s="25"/>
+      <c r="C176" s="24"/>
+      <c r="D176" s="25"/>
       <c r="E176" s="18"/>
       <c r="F176" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G176" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H176" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I176" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J176" s="20"/>
       <c r="K176" s="2"/>
       <c r="L176" s="2"/>
       <c r="M176" s="18"/>
       <c r="N176" s="18"/>
-      <c r="O176" s="57"/>
-      <c r="P176" s="58"/>
+      <c r="O176" s="24"/>
+      <c r="P176" s="25"/>
       <c r="Q176" s="3"/>
     </row>
     <row r="177" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A177" s="59"/>
-      <c r="B177" s="60"/>
-      <c r="C177" s="59"/>
-      <c r="D177" s="60"/>
+      <c r="A177" s="26"/>
+      <c r="B177" s="27"/>
+      <c r="C177" s="26"/>
+      <c r="D177" s="27"/>
       <c r="E177" s="21"/>
       <c r="F177" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G177" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H177" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I177" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J177" s="22"/>
       <c r="K177" s="23"/>
       <c r="L177" s="23"/>
       <c r="M177" s="21"/>
       <c r="N177" s="21"/>
-      <c r="O177" s="59"/>
-      <c r="P177" s="60"/>
+      <c r="O177" s="26"/>
+      <c r="P177" s="27"/>
       <c r="Q177" s="23"/>
     </row>
     <row r="178" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="57"/>
-      <c r="B178" s="58"/>
-      <c r="C178" s="57"/>
-      <c r="D178" s="58"/>
+      <c r="A178" s="24"/>
+      <c r="B178" s="25"/>
+      <c r="C178" s="24"/>
+      <c r="D178" s="25"/>
       <c r="E178" s="18"/>
       <c r="F178" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G178" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H178" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I178" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J178" s="20"/>
       <c r="K178" s="2"/>
       <c r="L178" s="2"/>
       <c r="M178" s="18"/>
       <c r="N178" s="18"/>
-      <c r="O178" s="57"/>
-      <c r="P178" s="58"/>
+      <c r="O178" s="24"/>
+      <c r="P178" s="25"/>
       <c r="Q178" s="3"/>
     </row>
     <row r="179" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A179" s="59"/>
-      <c r="B179" s="60"/>
-      <c r="C179" s="59"/>
-      <c r="D179" s="60"/>
+      <c r="A179" s="26"/>
+      <c r="B179" s="27"/>
+      <c r="C179" s="26"/>
+      <c r="D179" s="27"/>
       <c r="E179" s="21"/>
       <c r="F179" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G179" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H179" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I179" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J179" s="22"/>
       <c r="K179" s="23"/>
       <c r="L179" s="23"/>
       <c r="M179" s="21"/>
       <c r="N179" s="21"/>
-      <c r="O179" s="59"/>
-      <c r="P179" s="60"/>
+      <c r="O179" s="26"/>
+      <c r="P179" s="27"/>
       <c r="Q179" s="23"/>
     </row>
     <row r="180" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="57"/>
-      <c r="B180" s="58"/>
-      <c r="C180" s="57"/>
-      <c r="D180" s="58"/>
+      <c r="A180" s="24"/>
+      <c r="B180" s="25"/>
+      <c r="C180" s="24"/>
+      <c r="D180" s="25"/>
       <c r="E180" s="18"/>
       <c r="F180" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G180" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H180" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I180" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J180" s="20"/>
       <c r="K180" s="2"/>
       <c r="L180" s="2"/>
       <c r="M180" s="18"/>
       <c r="N180" s="18"/>
-      <c r="O180" s="57"/>
-      <c r="P180" s="58"/>
+      <c r="O180" s="24"/>
+      <c r="P180" s="25"/>
       <c r="Q180" s="3"/>
     </row>
     <row r="181" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A181" s="59"/>
-      <c r="B181" s="60"/>
-      <c r="C181" s="59"/>
-      <c r="D181" s="60"/>
+      <c r="A181" s="26"/>
+      <c r="B181" s="27"/>
+      <c r="C181" s="26"/>
+      <c r="D181" s="27"/>
       <c r="E181" s="21"/>
       <c r="F181" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G181" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H181" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I181" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J181" s="22"/>
       <c r="K181" s="23"/>
       <c r="L181" s="23"/>
       <c r="M181" s="21"/>
       <c r="N181" s="21"/>
-      <c r="O181" s="59"/>
-      <c r="P181" s="60"/>
+      <c r="O181" s="26"/>
+      <c r="P181" s="27"/>
       <c r="Q181" s="23"/>
     </row>
     <row r="182" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="57"/>
-      <c r="B182" s="58"/>
-      <c r="C182" s="57"/>
-      <c r="D182" s="58"/>
+      <c r="A182" s="24"/>
+      <c r="B182" s="25"/>
+      <c r="C182" s="24"/>
+      <c r="D182" s="25"/>
       <c r="E182" s="18"/>
       <c r="F182" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G182" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H182" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I182" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J182" s="20"/>
       <c r="K182" s="2"/>
       <c r="L182" s="2"/>
       <c r="M182" s="18"/>
       <c r="N182" s="18"/>
-      <c r="O182" s="57"/>
-      <c r="P182" s="58"/>
+      <c r="O182" s="24"/>
+      <c r="P182" s="25"/>
       <c r="Q182" s="3"/>
     </row>
     <row r="183" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A183" s="59"/>
-      <c r="B183" s="60"/>
-      <c r="C183" s="59"/>
-      <c r="D183" s="60"/>
+      <c r="A183" s="26"/>
+      <c r="B183" s="27"/>
+      <c r="C183" s="26"/>
+      <c r="D183" s="27"/>
       <c r="E183" s="21"/>
       <c r="F183" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G183" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H183" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I183" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J183" s="22"/>
       <c r="K183" s="23"/>
       <c r="L183" s="23"/>
       <c r="M183" s="21"/>
       <c r="N183" s="21"/>
-      <c r="O183" s="59"/>
-      <c r="P183" s="60"/>
+      <c r="O183" s="26"/>
+      <c r="P183" s="27"/>
       <c r="Q183" s="23"/>
     </row>
     <row r="184" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A184" s="57"/>
-      <c r="B184" s="58"/>
-      <c r="C184" s="57"/>
-      <c r="D184" s="58"/>
+      <c r="A184" s="24"/>
+      <c r="B184" s="25"/>
+      <c r="C184" s="24"/>
+      <c r="D184" s="25"/>
       <c r="E184" s="18"/>
       <c r="F184" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G184" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H184" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I184" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J184" s="20"/>
       <c r="K184" s="2"/>
       <c r="L184" s="2"/>
       <c r="M184" s="18"/>
       <c r="N184" s="18"/>
-      <c r="O184" s="57"/>
-      <c r="P184" s="58"/>
+      <c r="O184" s="24"/>
+      <c r="P184" s="25"/>
       <c r="Q184" s="3"/>
     </row>
     <row r="185" spans="1:17" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A185" s="59"/>
-      <c r="B185" s="60"/>
-      <c r="C185" s="59"/>
-      <c r="D185" s="60"/>
+      <c r="A185" s="26"/>
+      <c r="B185" s="27"/>
+      <c r="C185" s="26"/>
+      <c r="D185" s="27"/>
       <c r="E185" s="21"/>
       <c r="F185" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G185" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H185" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I185" s="22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J185" s="22"/>
       <c r="K185" s="23"/>
       <c r="L185" s="23"/>
       <c r="M185" s="21"/>
       <c r="N185" s="21"/>
-      <c r="O185" s="59"/>
-      <c r="P185" s="60"/>
+      <c r="O185" s="26"/>
+      <c r="P185" s="27"/>
       <c r="Q185" s="23"/>
     </row>
     <row r="186" spans="1:17" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="57"/>
-      <c r="B186" s="58"/>
-      <c r="C186" s="57"/>
-      <c r="D186" s="58"/>
+      <c r="A186" s="24"/>
+      <c r="B186" s="25"/>
+      <c r="C186" s="24"/>
+      <c r="D186" s="25"/>
       <c r="E186" s="18"/>
       <c r="F186" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G186" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H186" s="19" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I186" s="20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J186" s="20"/>
       <c r="K186" s="2"/>
       <c r="L186" s="2"/>
       <c r="M186" s="18"/>
       <c r="N186" s="18"/>
-      <c r="O186" s="57"/>
-      <c r="P186" s="58"/>
+      <c r="O186" s="24"/>
+      <c r="P186" s="25"/>
       <c r="Q186" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="543">
-    <mergeCell ref="A184:B184"/>
-    <mergeCell ref="C184:D184"/>
-    <mergeCell ref="O184:P184"/>
-    <mergeCell ref="A185:B185"/>
-    <mergeCell ref="C185:D185"/>
-    <mergeCell ref="O185:P185"/>
-    <mergeCell ref="A186:B186"/>
-    <mergeCell ref="C186:D186"/>
-    <mergeCell ref="O186:P186"/>
-    <mergeCell ref="A181:B181"/>
-    <mergeCell ref="C181:D181"/>
-    <mergeCell ref="O181:P181"/>
-    <mergeCell ref="A182:B182"/>
-    <mergeCell ref="C182:D182"/>
-    <mergeCell ref="O182:P182"/>
-    <mergeCell ref="A183:B183"/>
-    <mergeCell ref="C183:D183"/>
-    <mergeCell ref="O183:P183"/>
-    <mergeCell ref="A178:B178"/>
-    <mergeCell ref="C178:D178"/>
-    <mergeCell ref="O178:P178"/>
-    <mergeCell ref="A179:B179"/>
-    <mergeCell ref="C179:D179"/>
-    <mergeCell ref="O179:P179"/>
-    <mergeCell ref="A180:B180"/>
-    <mergeCell ref="C180:D180"/>
-    <mergeCell ref="O180:P180"/>
-    <mergeCell ref="A175:B175"/>
-    <mergeCell ref="C175:D175"/>
-    <mergeCell ref="O175:P175"/>
-    <mergeCell ref="A176:B176"/>
-    <mergeCell ref="C176:D176"/>
-    <mergeCell ref="O176:P176"/>
-    <mergeCell ref="A177:B177"/>
-    <mergeCell ref="C177:D177"/>
-    <mergeCell ref="O177:P177"/>
-    <mergeCell ref="A172:B172"/>
-    <mergeCell ref="C172:D172"/>
-    <mergeCell ref="O172:P172"/>
-    <mergeCell ref="A173:B173"/>
-    <mergeCell ref="C173:D173"/>
-    <mergeCell ref="O173:P173"/>
-    <mergeCell ref="A174:B174"/>
-    <mergeCell ref="C174:D174"/>
-    <mergeCell ref="O174:P174"/>
-    <mergeCell ref="A169:B169"/>
-    <mergeCell ref="C169:D169"/>
-    <mergeCell ref="O169:P169"/>
-    <mergeCell ref="A170:B170"/>
-    <mergeCell ref="C170:D170"/>
-    <mergeCell ref="O170:P170"/>
-    <mergeCell ref="A171:B171"/>
-    <mergeCell ref="C171:D171"/>
-    <mergeCell ref="O171:P171"/>
-    <mergeCell ref="A166:B166"/>
-    <mergeCell ref="C166:D166"/>
-    <mergeCell ref="O166:P166"/>
-    <mergeCell ref="A167:B167"/>
-    <mergeCell ref="C167:D167"/>
-    <mergeCell ref="O167:P167"/>
-    <mergeCell ref="A168:B168"/>
-    <mergeCell ref="C168:D168"/>
-    <mergeCell ref="O168:P168"/>
-    <mergeCell ref="A163:B163"/>
-    <mergeCell ref="C163:D163"/>
-    <mergeCell ref="O163:P163"/>
-    <mergeCell ref="A164:B164"/>
-    <mergeCell ref="C164:D164"/>
-    <mergeCell ref="O164:P164"/>
-    <mergeCell ref="A165:B165"/>
-    <mergeCell ref="C165:D165"/>
-    <mergeCell ref="O165:P165"/>
-    <mergeCell ref="A160:B160"/>
-    <mergeCell ref="C160:D160"/>
-    <mergeCell ref="O160:P160"/>
-    <mergeCell ref="A161:B161"/>
-    <mergeCell ref="C161:D161"/>
-    <mergeCell ref="O161:P161"/>
-    <mergeCell ref="A162:B162"/>
-    <mergeCell ref="C162:D162"/>
-    <mergeCell ref="O162:P162"/>
-    <mergeCell ref="A157:B157"/>
-    <mergeCell ref="C157:D157"/>
-    <mergeCell ref="O157:P157"/>
-    <mergeCell ref="A158:B158"/>
-    <mergeCell ref="C158:D158"/>
-    <mergeCell ref="O158:P158"/>
-    <mergeCell ref="A159:B159"/>
-    <mergeCell ref="C159:D159"/>
-    <mergeCell ref="O159:P159"/>
-    <mergeCell ref="A154:B154"/>
-    <mergeCell ref="C154:D154"/>
-    <mergeCell ref="O154:P154"/>
-    <mergeCell ref="A155:B155"/>
-    <mergeCell ref="C155:D155"/>
-    <mergeCell ref="O155:P155"/>
-    <mergeCell ref="A156:B156"/>
-    <mergeCell ref="C156:D156"/>
-    <mergeCell ref="O156:P156"/>
-    <mergeCell ref="A151:B151"/>
-    <mergeCell ref="C151:D151"/>
-    <mergeCell ref="O151:P151"/>
-    <mergeCell ref="A152:B152"/>
-    <mergeCell ref="C152:D152"/>
-    <mergeCell ref="O152:P152"/>
-    <mergeCell ref="A153:B153"/>
-    <mergeCell ref="C153:D153"/>
-    <mergeCell ref="O153:P153"/>
-    <mergeCell ref="A148:B148"/>
-    <mergeCell ref="C148:D148"/>
-    <mergeCell ref="O148:P148"/>
-    <mergeCell ref="A149:B149"/>
-    <mergeCell ref="C149:D149"/>
-    <mergeCell ref="O149:P149"/>
-    <mergeCell ref="A150:B150"/>
-    <mergeCell ref="C150:D150"/>
-    <mergeCell ref="O150:P150"/>
-    <mergeCell ref="A145:B145"/>
-    <mergeCell ref="C145:D145"/>
-    <mergeCell ref="O145:P145"/>
-    <mergeCell ref="A146:B146"/>
-    <mergeCell ref="C146:D146"/>
-    <mergeCell ref="O146:P146"/>
-    <mergeCell ref="A147:B147"/>
-    <mergeCell ref="C147:D147"/>
-    <mergeCell ref="O147:P147"/>
-    <mergeCell ref="A142:B142"/>
-    <mergeCell ref="C142:D142"/>
-    <mergeCell ref="O142:P142"/>
-    <mergeCell ref="A143:B143"/>
-    <mergeCell ref="C143:D143"/>
-    <mergeCell ref="O143:P143"/>
-    <mergeCell ref="A144:B144"/>
-    <mergeCell ref="C144:D144"/>
-    <mergeCell ref="O144:P144"/>
-    <mergeCell ref="A139:B139"/>
-    <mergeCell ref="C139:D139"/>
-    <mergeCell ref="O139:P139"/>
-    <mergeCell ref="A140:B140"/>
-    <mergeCell ref="C140:D140"/>
-    <mergeCell ref="O140:P140"/>
-    <mergeCell ref="A141:B141"/>
-    <mergeCell ref="C141:D141"/>
-    <mergeCell ref="O141:P141"/>
-    <mergeCell ref="A136:B136"/>
-    <mergeCell ref="C136:D136"/>
-    <mergeCell ref="O136:P136"/>
-    <mergeCell ref="A137:B137"/>
-    <mergeCell ref="C137:D137"/>
-    <mergeCell ref="O137:P137"/>
-    <mergeCell ref="A138:B138"/>
-    <mergeCell ref="C138:D138"/>
-    <mergeCell ref="O138:P138"/>
-    <mergeCell ref="A133:B133"/>
-    <mergeCell ref="C133:D133"/>
-    <mergeCell ref="O133:P133"/>
-    <mergeCell ref="A134:B134"/>
-    <mergeCell ref="C134:D134"/>
-    <mergeCell ref="O134:P134"/>
-    <mergeCell ref="A135:B135"/>
-    <mergeCell ref="C135:D135"/>
-    <mergeCell ref="O135:P135"/>
-    <mergeCell ref="A130:B130"/>
-    <mergeCell ref="C130:D130"/>
-    <mergeCell ref="O130:P130"/>
-    <mergeCell ref="A131:B131"/>
-    <mergeCell ref="C131:D131"/>
-    <mergeCell ref="O131:P131"/>
-    <mergeCell ref="A132:B132"/>
-    <mergeCell ref="C132:D132"/>
-    <mergeCell ref="O132:P132"/>
-    <mergeCell ref="A127:B127"/>
-    <mergeCell ref="C127:D127"/>
-    <mergeCell ref="O127:P127"/>
-    <mergeCell ref="A128:B128"/>
-    <mergeCell ref="C128:D128"/>
-    <mergeCell ref="O128:P128"/>
-    <mergeCell ref="A129:B129"/>
-    <mergeCell ref="C129:D129"/>
-    <mergeCell ref="O129:P129"/>
-    <mergeCell ref="A124:B124"/>
-    <mergeCell ref="C124:D124"/>
-    <mergeCell ref="O124:P124"/>
-    <mergeCell ref="A125:B125"/>
-    <mergeCell ref="C125:D125"/>
-    <mergeCell ref="O125:P125"/>
-    <mergeCell ref="A126:B126"/>
-    <mergeCell ref="C126:D126"/>
-    <mergeCell ref="O126:P126"/>
-    <mergeCell ref="A121:B121"/>
-    <mergeCell ref="C121:D121"/>
-    <mergeCell ref="O121:P121"/>
-    <mergeCell ref="A122:B122"/>
-    <mergeCell ref="C122:D122"/>
-    <mergeCell ref="O122:P122"/>
-    <mergeCell ref="A123:B123"/>
-    <mergeCell ref="C123:D123"/>
-    <mergeCell ref="O123:P123"/>
-    <mergeCell ref="A118:B118"/>
-    <mergeCell ref="C118:D118"/>
-    <mergeCell ref="O118:P118"/>
-    <mergeCell ref="A119:B119"/>
-    <mergeCell ref="C119:D119"/>
-    <mergeCell ref="O119:P119"/>
-    <mergeCell ref="A120:B120"/>
-    <mergeCell ref="C120:D120"/>
-    <mergeCell ref="O120:P120"/>
-    <mergeCell ref="A115:B115"/>
-    <mergeCell ref="C115:D115"/>
-    <mergeCell ref="O115:P115"/>
-    <mergeCell ref="A116:B116"/>
-    <mergeCell ref="C116:D116"/>
-    <mergeCell ref="O116:P116"/>
-    <mergeCell ref="A117:B117"/>
-    <mergeCell ref="C117:D117"/>
-    <mergeCell ref="O117:P117"/>
-    <mergeCell ref="A112:B112"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="O112:P112"/>
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="O113:P113"/>
-    <mergeCell ref="A114:B114"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="O114:P114"/>
-    <mergeCell ref="A109:B109"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="O109:P109"/>
-    <mergeCell ref="A110:B110"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="O110:P110"/>
-    <mergeCell ref="A111:B111"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="O111:P111"/>
-    <mergeCell ref="A106:B106"/>
-    <mergeCell ref="C106:D106"/>
-    <mergeCell ref="O106:P106"/>
-    <mergeCell ref="A107:B107"/>
-    <mergeCell ref="C107:D107"/>
-    <mergeCell ref="O107:P107"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="O108:P108"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="O103:P103"/>
-    <mergeCell ref="A104:B104"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="O104:P104"/>
-    <mergeCell ref="A105:B105"/>
-    <mergeCell ref="C105:D105"/>
-    <mergeCell ref="O105:P105"/>
-    <mergeCell ref="A100:B100"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="O100:P100"/>
-    <mergeCell ref="A101:B101"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="O101:P101"/>
-    <mergeCell ref="A102:B102"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="O102:P102"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="O97:P97"/>
-    <mergeCell ref="A98:B98"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="O98:P98"/>
-    <mergeCell ref="A99:B99"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="O99:P99"/>
-    <mergeCell ref="A94:B94"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="O94:P94"/>
-    <mergeCell ref="A95:B95"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="O95:P95"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="O96:P96"/>
-    <mergeCell ref="A91:B91"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="O91:P91"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="O92:P92"/>
-    <mergeCell ref="A93:B93"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="O93:P93"/>
-    <mergeCell ref="A88:B88"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="O88:P88"/>
-    <mergeCell ref="A89:B89"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="O89:P89"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="O90:P90"/>
-    <mergeCell ref="A85:B85"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="O85:P85"/>
-    <mergeCell ref="A86:B86"/>
-    <mergeCell ref="C86:D86"/>
-    <mergeCell ref="O86:P86"/>
-    <mergeCell ref="A87:B87"/>
-    <mergeCell ref="C87:D87"/>
-    <mergeCell ref="O87:P87"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="O82:P82"/>
-    <mergeCell ref="A83:B83"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="O83:P83"/>
-    <mergeCell ref="A84:B84"/>
-    <mergeCell ref="C84:D84"/>
-    <mergeCell ref="O84:P84"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="O79:P79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="O80:P80"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="O81:P81"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="O76:P76"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="O77:P77"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="O78:P78"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="O73:P73"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="O74:P74"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="O75:P75"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="O70:P70"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="O71:P71"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="O72:P72"/>
-    <mergeCell ref="A67:B67"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="O67:P67"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="O68:P68"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="O69:P69"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="O64:P64"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="O65:P65"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="O66:P66"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="O61:P61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="O62:P62"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="O63:P63"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="O58:P58"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="O59:P59"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="O60:P60"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="O55:P55"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="O56:P56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="O57:P57"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="O52:P52"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="O53:P53"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="O54:P54"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="O49:P49"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="O50:P50"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="O51:P51"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="O46:P46"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="O47:P47"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="O48:P48"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="O43:P43"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="O44:P44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="O45:P45"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="O41:P41"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="O42:P42"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="O37:P37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="O34:P34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="O35:P35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="O36:P36"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="O31:P31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="O32:P32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="O33:P33"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="O28:P28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="O29:P29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="O30:P30"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="O25:P25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="O26:P26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="O27:P27"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="O22:P22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="O23:P23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="O24:P24"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="O16:P16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="O13:P13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="O14:P14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="O15:P15"/>
-    <mergeCell ref="A10:B11"/>
-    <mergeCell ref="C10:D11"/>
-    <mergeCell ref="F10:L10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="O10:P11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="O12:P12"/>
     <mergeCell ref="A1:B4"/>
     <mergeCell ref="C1:M4"/>
     <mergeCell ref="N1:O1"/>
@@ -6803,6 +6191,537 @@
     <mergeCell ref="K7:P7"/>
     <mergeCell ref="K8:M9"/>
     <mergeCell ref="N8:P9"/>
+    <mergeCell ref="A10:B11"/>
+    <mergeCell ref="C10:D11"/>
+    <mergeCell ref="F10:L10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="O10:P11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="O12:P12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="O13:P13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="O14:P14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="O15:P15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="O16:P16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="O22:P22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="O23:P23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="O24:P24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="O25:P25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="O27:P27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="O28:P28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="O29:P29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="O31:P31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="O35:P35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="O36:P36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="O37:P37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="O41:P41"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="O42:P42"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="O43:P43"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="O44:P44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="O45:P45"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="O46:P46"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="O47:P47"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="O48:P48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="O49:P49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="O50:P50"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="O51:P51"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="O52:P52"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="O53:P53"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="O54:P54"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="O55:P55"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="O56:P56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="O57:P57"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="O58:P58"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="O59:P59"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="O60:P60"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="O61:P61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="O62:P62"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="O63:P63"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="O64:P64"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="O65:P65"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="O66:P66"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="O67:P67"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="O68:P68"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="O69:P69"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="O70:P70"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="O71:P71"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="O72:P72"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="O73:P73"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="O74:P74"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="O75:P75"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="O76:P76"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="O77:P77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="O78:P78"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="O79:P79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="O80:P80"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="O81:P81"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="O82:P82"/>
+    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="O83:P83"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="O84:P84"/>
+    <mergeCell ref="A85:B85"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="O85:P85"/>
+    <mergeCell ref="A86:B86"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="O86:P86"/>
+    <mergeCell ref="A87:B87"/>
+    <mergeCell ref="C87:D87"/>
+    <mergeCell ref="O87:P87"/>
+    <mergeCell ref="A88:B88"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="O88:P88"/>
+    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="O89:P89"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="O90:P90"/>
+    <mergeCell ref="A91:B91"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="O91:P91"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="O92:P92"/>
+    <mergeCell ref="A93:B93"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="O93:P93"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="O94:P94"/>
+    <mergeCell ref="A95:B95"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="O95:P95"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="O96:P96"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="O97:P97"/>
+    <mergeCell ref="A98:B98"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="O98:P98"/>
+    <mergeCell ref="A99:B99"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="O99:P99"/>
+    <mergeCell ref="A100:B100"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="O100:P100"/>
+    <mergeCell ref="A101:B101"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="O101:P101"/>
+    <mergeCell ref="A102:B102"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="O102:P102"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="O103:P103"/>
+    <mergeCell ref="A104:B104"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="O104:P104"/>
+    <mergeCell ref="A105:B105"/>
+    <mergeCell ref="C105:D105"/>
+    <mergeCell ref="O105:P105"/>
+    <mergeCell ref="A106:B106"/>
+    <mergeCell ref="C106:D106"/>
+    <mergeCell ref="O106:P106"/>
+    <mergeCell ref="A107:B107"/>
+    <mergeCell ref="C107:D107"/>
+    <mergeCell ref="O107:P107"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="O108:P108"/>
+    <mergeCell ref="A109:B109"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="O109:P109"/>
+    <mergeCell ref="A110:B110"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="O110:P110"/>
+    <mergeCell ref="A111:B111"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="O111:P111"/>
+    <mergeCell ref="A112:B112"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="O112:P112"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="O113:P113"/>
+    <mergeCell ref="A114:B114"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="O114:P114"/>
+    <mergeCell ref="A115:B115"/>
+    <mergeCell ref="C115:D115"/>
+    <mergeCell ref="O115:P115"/>
+    <mergeCell ref="A116:B116"/>
+    <mergeCell ref="C116:D116"/>
+    <mergeCell ref="O116:P116"/>
+    <mergeCell ref="A117:B117"/>
+    <mergeCell ref="C117:D117"/>
+    <mergeCell ref="O117:P117"/>
+    <mergeCell ref="A118:B118"/>
+    <mergeCell ref="C118:D118"/>
+    <mergeCell ref="O118:P118"/>
+    <mergeCell ref="A119:B119"/>
+    <mergeCell ref="C119:D119"/>
+    <mergeCell ref="O119:P119"/>
+    <mergeCell ref="A120:B120"/>
+    <mergeCell ref="C120:D120"/>
+    <mergeCell ref="O120:P120"/>
+    <mergeCell ref="A121:B121"/>
+    <mergeCell ref="C121:D121"/>
+    <mergeCell ref="O121:P121"/>
+    <mergeCell ref="A122:B122"/>
+    <mergeCell ref="C122:D122"/>
+    <mergeCell ref="O122:P122"/>
+    <mergeCell ref="A123:B123"/>
+    <mergeCell ref="C123:D123"/>
+    <mergeCell ref="O123:P123"/>
+    <mergeCell ref="A124:B124"/>
+    <mergeCell ref="C124:D124"/>
+    <mergeCell ref="O124:P124"/>
+    <mergeCell ref="A125:B125"/>
+    <mergeCell ref="C125:D125"/>
+    <mergeCell ref="O125:P125"/>
+    <mergeCell ref="A126:B126"/>
+    <mergeCell ref="C126:D126"/>
+    <mergeCell ref="O126:P126"/>
+    <mergeCell ref="A127:B127"/>
+    <mergeCell ref="C127:D127"/>
+    <mergeCell ref="O127:P127"/>
+    <mergeCell ref="A128:B128"/>
+    <mergeCell ref="C128:D128"/>
+    <mergeCell ref="O128:P128"/>
+    <mergeCell ref="A129:B129"/>
+    <mergeCell ref="C129:D129"/>
+    <mergeCell ref="O129:P129"/>
+    <mergeCell ref="A130:B130"/>
+    <mergeCell ref="C130:D130"/>
+    <mergeCell ref="O130:P130"/>
+    <mergeCell ref="A131:B131"/>
+    <mergeCell ref="C131:D131"/>
+    <mergeCell ref="O131:P131"/>
+    <mergeCell ref="A132:B132"/>
+    <mergeCell ref="C132:D132"/>
+    <mergeCell ref="O132:P132"/>
+    <mergeCell ref="A133:B133"/>
+    <mergeCell ref="C133:D133"/>
+    <mergeCell ref="O133:P133"/>
+    <mergeCell ref="A134:B134"/>
+    <mergeCell ref="C134:D134"/>
+    <mergeCell ref="O134:P134"/>
+    <mergeCell ref="A135:B135"/>
+    <mergeCell ref="C135:D135"/>
+    <mergeCell ref="O135:P135"/>
+    <mergeCell ref="A136:B136"/>
+    <mergeCell ref="C136:D136"/>
+    <mergeCell ref="O136:P136"/>
+    <mergeCell ref="A137:B137"/>
+    <mergeCell ref="C137:D137"/>
+    <mergeCell ref="O137:P137"/>
+    <mergeCell ref="A138:B138"/>
+    <mergeCell ref="C138:D138"/>
+    <mergeCell ref="O138:P138"/>
+    <mergeCell ref="A139:B139"/>
+    <mergeCell ref="C139:D139"/>
+    <mergeCell ref="O139:P139"/>
+    <mergeCell ref="A140:B140"/>
+    <mergeCell ref="C140:D140"/>
+    <mergeCell ref="O140:P140"/>
+    <mergeCell ref="A141:B141"/>
+    <mergeCell ref="C141:D141"/>
+    <mergeCell ref="O141:P141"/>
+    <mergeCell ref="A142:B142"/>
+    <mergeCell ref="C142:D142"/>
+    <mergeCell ref="O142:P142"/>
+    <mergeCell ref="A143:B143"/>
+    <mergeCell ref="C143:D143"/>
+    <mergeCell ref="O143:P143"/>
+    <mergeCell ref="A144:B144"/>
+    <mergeCell ref="C144:D144"/>
+    <mergeCell ref="O144:P144"/>
+    <mergeCell ref="A145:B145"/>
+    <mergeCell ref="C145:D145"/>
+    <mergeCell ref="O145:P145"/>
+    <mergeCell ref="A146:B146"/>
+    <mergeCell ref="C146:D146"/>
+    <mergeCell ref="O146:P146"/>
+    <mergeCell ref="A147:B147"/>
+    <mergeCell ref="C147:D147"/>
+    <mergeCell ref="O147:P147"/>
+    <mergeCell ref="A148:B148"/>
+    <mergeCell ref="C148:D148"/>
+    <mergeCell ref="O148:P148"/>
+    <mergeCell ref="A149:B149"/>
+    <mergeCell ref="C149:D149"/>
+    <mergeCell ref="O149:P149"/>
+    <mergeCell ref="A150:B150"/>
+    <mergeCell ref="C150:D150"/>
+    <mergeCell ref="O150:P150"/>
+    <mergeCell ref="A151:B151"/>
+    <mergeCell ref="C151:D151"/>
+    <mergeCell ref="O151:P151"/>
+    <mergeCell ref="A152:B152"/>
+    <mergeCell ref="C152:D152"/>
+    <mergeCell ref="O152:P152"/>
+    <mergeCell ref="A153:B153"/>
+    <mergeCell ref="C153:D153"/>
+    <mergeCell ref="O153:P153"/>
+    <mergeCell ref="A154:B154"/>
+    <mergeCell ref="C154:D154"/>
+    <mergeCell ref="O154:P154"/>
+    <mergeCell ref="A155:B155"/>
+    <mergeCell ref="C155:D155"/>
+    <mergeCell ref="O155:P155"/>
+    <mergeCell ref="A156:B156"/>
+    <mergeCell ref="C156:D156"/>
+    <mergeCell ref="O156:P156"/>
+    <mergeCell ref="A157:B157"/>
+    <mergeCell ref="C157:D157"/>
+    <mergeCell ref="O157:P157"/>
+    <mergeCell ref="A158:B158"/>
+    <mergeCell ref="C158:D158"/>
+    <mergeCell ref="O158:P158"/>
+    <mergeCell ref="A159:B159"/>
+    <mergeCell ref="C159:D159"/>
+    <mergeCell ref="O159:P159"/>
+    <mergeCell ref="A160:B160"/>
+    <mergeCell ref="C160:D160"/>
+    <mergeCell ref="O160:P160"/>
+    <mergeCell ref="A161:B161"/>
+    <mergeCell ref="C161:D161"/>
+    <mergeCell ref="O161:P161"/>
+    <mergeCell ref="A162:B162"/>
+    <mergeCell ref="C162:D162"/>
+    <mergeCell ref="O162:P162"/>
+    <mergeCell ref="A163:B163"/>
+    <mergeCell ref="C163:D163"/>
+    <mergeCell ref="O163:P163"/>
+    <mergeCell ref="A164:B164"/>
+    <mergeCell ref="C164:D164"/>
+    <mergeCell ref="O164:P164"/>
+    <mergeCell ref="A165:B165"/>
+    <mergeCell ref="C165:D165"/>
+    <mergeCell ref="O165:P165"/>
+    <mergeCell ref="A166:B166"/>
+    <mergeCell ref="C166:D166"/>
+    <mergeCell ref="O166:P166"/>
+    <mergeCell ref="A167:B167"/>
+    <mergeCell ref="C167:D167"/>
+    <mergeCell ref="O167:P167"/>
+    <mergeCell ref="A168:B168"/>
+    <mergeCell ref="C168:D168"/>
+    <mergeCell ref="O168:P168"/>
+    <mergeCell ref="A169:B169"/>
+    <mergeCell ref="C169:D169"/>
+    <mergeCell ref="O169:P169"/>
+    <mergeCell ref="A170:B170"/>
+    <mergeCell ref="C170:D170"/>
+    <mergeCell ref="O170:P170"/>
+    <mergeCell ref="A171:B171"/>
+    <mergeCell ref="C171:D171"/>
+    <mergeCell ref="O171:P171"/>
+    <mergeCell ref="A172:B172"/>
+    <mergeCell ref="C172:D172"/>
+    <mergeCell ref="O172:P172"/>
+    <mergeCell ref="A173:B173"/>
+    <mergeCell ref="C173:D173"/>
+    <mergeCell ref="O173:P173"/>
+    <mergeCell ref="A174:B174"/>
+    <mergeCell ref="C174:D174"/>
+    <mergeCell ref="O174:P174"/>
+    <mergeCell ref="A175:B175"/>
+    <mergeCell ref="C175:D175"/>
+    <mergeCell ref="O175:P175"/>
+    <mergeCell ref="A176:B176"/>
+    <mergeCell ref="C176:D176"/>
+    <mergeCell ref="O176:P176"/>
+    <mergeCell ref="A177:B177"/>
+    <mergeCell ref="C177:D177"/>
+    <mergeCell ref="O177:P177"/>
+    <mergeCell ref="A178:B178"/>
+    <mergeCell ref="C178:D178"/>
+    <mergeCell ref="O178:P178"/>
+    <mergeCell ref="A179:B179"/>
+    <mergeCell ref="C179:D179"/>
+    <mergeCell ref="O179:P179"/>
+    <mergeCell ref="A180:B180"/>
+    <mergeCell ref="C180:D180"/>
+    <mergeCell ref="O180:P180"/>
+    <mergeCell ref="A181:B181"/>
+    <mergeCell ref="C181:D181"/>
+    <mergeCell ref="O181:P181"/>
+    <mergeCell ref="A182:B182"/>
+    <mergeCell ref="C182:D182"/>
+    <mergeCell ref="O182:P182"/>
+    <mergeCell ref="A183:B183"/>
+    <mergeCell ref="C183:D183"/>
+    <mergeCell ref="O183:P183"/>
+    <mergeCell ref="A184:B184"/>
+    <mergeCell ref="C184:D184"/>
+    <mergeCell ref="O184:P184"/>
+    <mergeCell ref="A185:B185"/>
+    <mergeCell ref="C185:D185"/>
+    <mergeCell ref="O185:P185"/>
+    <mergeCell ref="A186:B186"/>
+    <mergeCell ref="C186:D186"/>
+    <mergeCell ref="O186:P186"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="landscape" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>

--- a/data/arac-kullanim-sablon.xlsx
+++ b/data/arac-kullanim-sablon.xlsx
@@ -588,52 +588,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>112058</colOff>
-      <row>1</row>
-      <rowOff>9536</rowOff>
-    </from>
-    <to>
-      <col>1</col>
-      <colOff>321236</colOff>
-      <row>2</row>
-      <rowOff>149412</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Resim 2"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="112058" y="196301"/>
-          <a:ext cx="1307354" cy="326640"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -8588,9 +8542,9 @@
     </row>
   </sheetData>
   <mergeCells count="543">
-    <mergeCell ref="A186:B186"/>
     <mergeCell ref="A64:B64"/>
     <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A186:B186"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="A51:B51"/>
     <mergeCell ref="A107:B107"/>
@@ -9134,6 +9088,5 @@
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" scale="10"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>